--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -489,10 +489,10 @@
         <v>77.7</v>
       </c>
       <c r="G2" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="H2" t="n">
-        <v>37.6</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="3">
@@ -517,10 +517,10 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>62.7</v>
+        <v>62.5</v>
       </c>
       <c r="H3" t="n">
-        <v>33.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="4">
@@ -570,10 +570,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>70.5</v>
+        <v>69.7</v>
       </c>
       <c r="G5" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
@@ -595,16 +595,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>67.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>40.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
@@ -791,7 +791,7 @@
         <v>27.6</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
         <v>0.7</v>
@@ -819,13 +819,13 @@
         <v>72.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="F14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
         <v>0.6</v>
@@ -1370,10 +1370,10 @@
         <v>89.2</v>
       </c>
       <c r="G2" t="n">
-        <v>75.2</v>
+        <v>75.8</v>
       </c>
       <c r="H2" t="n">
-        <v>60.6</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="3">
@@ -1395,13 +1395,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>56.4</v>
+        <v>55.6</v>
       </c>
       <c r="G3" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>12.2</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="4">
@@ -1423,13 +1423,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>55.3</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
@@ -1454,7 +1454,7 @@
         <v>62.8</v>
       </c>
       <c r="G5" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="H5" t="n">
         <v>7.1</v>
@@ -1504,16 +1504,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="F7" t="n">
-        <v>31.1</v>
+        <v>29.3</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -1532,13 +1532,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>76.2</v>
+        <v>78.5</v>
       </c>
       <c r="F8" t="n">
-        <v>39.5</v>
+        <v>40.6</v>
       </c>
       <c r="G8" t="n">
-        <v>27.7</v>
+        <v>28.4</v>
       </c>
       <c r="H8" t="n">
         <v>8.300000000000001</v>
@@ -1616,10 +1616,10 @@
         <v>63.3</v>
       </c>
       <c r="E11" t="n">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
       <c r="F11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
         <v>0.9</v>
@@ -1641,19 +1641,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>64.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="E12" t="n">
-        <v>28.6</v>
+        <v>27.4</v>
       </c>
       <c r="F12" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -1678,7 +1678,7 @@
         <v>5.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="n">
         <v>0.2</v>
@@ -1725,16 +1725,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>35.9</v>
+        <v>36.4</v>
       </c>
       <c r="E15" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
@@ -1843,13 +1843,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>79.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>56.2</v>
+        <v>61.1</v>
       </c>
       <c r="H2" t="n">
-        <v>35.9</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="3">
@@ -1871,13 +1871,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>82.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G3" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="H3" t="n">
-        <v>26.8</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="4">
@@ -1899,13 +1899,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
       <c r="G4" t="n">
-        <v>38.8</v>
+        <v>37.8</v>
       </c>
       <c r="H4" t="n">
-        <v>15.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="5">
@@ -1927,13 +1927,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>43.9</v>
+        <v>44.7</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>12.3</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6">
@@ -1952,16 +1952,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>77.8</v>
+        <v>77.2</v>
       </c>
       <c r="F6" t="n">
-        <v>50.1</v>
+        <v>49.2</v>
       </c>
       <c r="G6" t="n">
-        <v>21.6</v>
+        <v>19.1</v>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1980,10 +1980,10 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="G7" t="n">
         <v>4.4</v>
@@ -2008,13 +2008,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>53.1</v>
+        <v>54.3</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
         <v>0.8</v>
@@ -2036,16 +2036,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>34.1</v>
+        <v>37.2</v>
       </c>
       <c r="F9" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -2061,19 +2061,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>85.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>60.5</v>
+        <v>56.4</v>
       </c>
       <c r="F10" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="G10" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -2089,19 +2089,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>76.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="E11" t="n">
-        <v>40.4</v>
+        <v>37.6</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -2148,16 +2148,16 @@
         <v>41.4</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
         <v>0.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -2204,10 +2204,10 @@
         <v>48.5</v>
       </c>
       <c r="E15" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
         <v>0.5</v>
@@ -2229,13 +2229,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>23.4</v>
+        <v>28.7</v>
       </c>
       <c r="E16" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -2257,16 +2257,16 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>17.1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2339,13 +2339,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>86.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>69.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G2" t="n">
-        <v>42.7</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="3">
@@ -2364,13 +2364,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>86.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>65.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>37.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="4">
@@ -2392,7 +2392,7 @@
         <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="G4" t="n">
         <v>9.699999999999999</v>
@@ -2417,10 +2417,10 @@
         <v>64.2</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
@@ -2442,10 +2442,10 @@
         <v>35.8</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -2467,10 +2467,10 @@
         <v>14.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -2539,13 +2539,13 @@
         <v>43.6</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
@@ -2564,13 +2564,13 @@
         <v>43.7</v>
       </c>
       <c r="E11" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -2592,10 +2592,10 @@
         <v>12.1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2684,10 +2684,10 @@
         <v>81.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="I2" t="n">
-        <v>32.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="3">
@@ -2712,13 +2712,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>71.2</v>
+        <v>64.7</v>
       </c>
       <c r="H3" t="n">
-        <v>34.9</v>
+        <v>29.5</v>
       </c>
       <c r="I3" t="n">
-        <v>12.6</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2746,10 +2746,10 @@
         <v>72.2</v>
       </c>
       <c r="H4" t="n">
-        <v>44.4</v>
+        <v>47.2</v>
       </c>
       <c r="I4" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="5">
@@ -2774,13 +2774,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>54.4</v>
+        <v>58</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>25.8</v>
       </c>
       <c r="I5" t="n">
-        <v>14.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="6">
@@ -2805,13 +2805,13 @@
         <v>84.2</v>
       </c>
       <c r="G6" t="n">
-        <v>42.6</v>
+        <v>40.1</v>
       </c>
       <c r="H6" t="n">
-        <v>20.2</v>
+        <v>18.9</v>
       </c>
       <c r="I6" t="n">
-        <v>12.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="7">
@@ -2839,7 +2839,7 @@
         <v>23.9</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="I7" t="n">
         <v>3.5</v>
@@ -2864,16 +2864,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>58.3</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>17.8</v>
+        <v>24.2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -2901,7 +2901,7 @@
         <v>11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
@@ -2923,19 +2923,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>73.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="G10" t="n">
         <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -2957,10 +2957,10 @@
         <v>62.8</v>
       </c>
       <c r="F11" t="n">
-        <v>29.7</v>
+        <v>27.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H11" t="n">
         <v>1.9</v>
@@ -2994,7 +2994,7 @@
         <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I12" t="n">
         <v>0.1</v>
@@ -3022,7 +3022,7 @@
         <v>5.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
@@ -3053,10 +3053,10 @@
         <v>10.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
         <v>0.1</v>
@@ -3112,10 +3112,10 @@
         <v>29.8</v>
       </c>
       <c r="F16" t="n">
-        <v>10.5</v>
+        <v>7.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H16" t="n">
         <v>0.5</v>
@@ -3137,19 +3137,19 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>59.8</v>
+        <v>57.1</v>
       </c>
       <c r="E17" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="F17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="G17" t="n">
         <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3168,13 +3168,13 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>40.2</v>
+        <v>42.9</v>
       </c>
       <c r="E18" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -3208,7 +3208,7 @@
         <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -3279,10 +3279,10 @@
         <v>84.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>61.9</v>
+        <v>62.3</v>
       </c>
       <c r="F2" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -3301,7 +3301,7 @@
         <v>96.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="F3" t="n">
         <v>56.8</v>
@@ -3323,10 +3323,10 @@
         <v>57.7</v>
       </c>
       <c r="E4" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="5">
@@ -3345,10 +3345,10 @@
         <v>71.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>27.1</v>
+        <v>25.4</v>
       </c>
       <c r="F5" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
@@ -3367,10 +3367,10 @@
         <v>28.1</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
@@ -3433,7 +3433,7 @@
         <v>15.4</v>
       </c>
       <c r="E9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -3832,13 +3832,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>81.2</v>
       </c>
       <c r="F2" t="n">
-        <v>61.2</v>
+        <v>59.8</v>
       </c>
       <c r="G2" t="n">
-        <v>40.6</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -3857,13 +3857,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>64.3</v>
       </c>
       <c r="F3" t="n">
-        <v>42.1</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4">
@@ -3882,13 +3882,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>67.8</v>
       </c>
       <c r="F4" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="G4" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3910,10 +3910,10 @@
         <v>49.1</v>
       </c>
       <c r="F5" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6">
@@ -3935,10 +3935,10 @@
         <v>50.9</v>
       </c>
       <c r="F6" t="n">
-        <v>16.5</v>
+        <v>16.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
@@ -3960,10 +3960,10 @@
         <v>30.9</v>
       </c>
       <c r="F7" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -3982,13 +3982,13 @@
         <v>77.2</v>
       </c>
       <c r="E8" t="n">
-        <v>28.4</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>13.9</v>
+        <v>16.2</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9">
@@ -4004,16 +4004,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>44.2</v>
+        <v>43.4</v>
       </c>
       <c r="E9" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -4029,16 +4029,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>55.8</v>
+        <v>56.6</v>
       </c>
       <c r="E10" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -4060,10 +4060,10 @@
         <v>3.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -4082,7 +4082,7 @@
         <v>12.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
         <v>0.1</v>
@@ -4191,13 +4191,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>72.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="G2" t="n">
-        <v>55.2</v>
+        <v>60.5</v>
       </c>
       <c r="H2" t="n">
-        <v>34.1</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="3">
@@ -4219,13 +4219,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>69.3</v>
+        <v>67.5</v>
       </c>
       <c r="G3" t="n">
-        <v>40.3</v>
+        <v>37.6</v>
       </c>
       <c r="H3" t="n">
-        <v>22.7</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="4">
@@ -4247,13 +4247,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="H4" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="5">
@@ -4275,13 +4275,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>37.9</v>
+        <v>38.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
@@ -4300,16 +4300,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>74.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>51</v>
+        <v>49.8</v>
       </c>
       <c r="G6" t="n">
-        <v>17.5</v>
+        <v>15.1</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -4334,10 +4334,10 @@
         <v>34.9</v>
       </c>
       <c r="G7" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="H7" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8">
@@ -4356,16 +4356,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>52.3</v>
+        <v>53.6</v>
       </c>
       <c r="F8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4384,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>69.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="F9" t="n">
-        <v>22.3</v>
+        <v>19.8</v>
       </c>
       <c r="G9" t="n">
-        <v>14.4</v>
+        <v>12.9</v>
       </c>
       <c r="H9" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="10">
@@ -4409,19 +4409,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>73.7</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4437,19 +4437,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="E11" t="n">
-        <v>37.4</v>
+        <v>37.9</v>
       </c>
       <c r="F11" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4471,13 +4471,13 @@
         <v>28.8</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -4524,16 +4524,16 @@
         <v>63.6</v>
       </c>
       <c r="E14" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -4555,7 +4555,7 @@
         <v>5.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
         <v>0.3</v>
@@ -4577,16 +4577,16 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>28.4</v>
+        <v>27.5</v>
       </c>
       <c r="E16" t="n">
-        <v>10.2</v>
+        <v>8.5</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
@@ -4605,13 +4605,13 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>26.3</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -26,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +54,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,42 +438,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -874,47 +886,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1307,42 +1319,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1783,42 +1795,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2287,37 +2299,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2613,47 +2625,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3232,32 +3244,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3454,37 +3466,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3780,37 +3792,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4131,42 +4143,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -26,16 +26,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +51,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,42 +426,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -498,13 +486,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.7</v>
+        <v>76.5</v>
       </c>
       <c r="G2" t="n">
-        <v>56.9</v>
+        <v>56</v>
       </c>
       <c r="H2" t="n">
-        <v>36.5</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="3">
@@ -529,10 +517,10 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>62.5</v>
+        <v>62.7</v>
       </c>
       <c r="H3" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="4">
@@ -557,10 +545,10 @@
         <v>48.4</v>
       </c>
       <c r="G4" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -582,10 +570,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>69.7</v>
+        <v>70.5</v>
       </c>
       <c r="G5" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
@@ -607,16 +595,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>68.3</v>
+        <v>68.8</v>
       </c>
       <c r="F6" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -635,16 +623,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="F7" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -672,7 +660,7 @@
         <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -681,7 +669,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>G Washington</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -691,16 +679,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>26.5</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>21.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>11.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
@@ -709,7 +697,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G Washington</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -719,16 +707,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>73.5</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>20.1</v>
+        <v>2.3</v>
       </c>
       <c r="G10" t="n">
-        <v>10.1</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -753,7 +741,7 @@
         <v>9.1</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H11" t="n">
         <v>0.8</v>
@@ -800,13 +788,13 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>27.6</v>
+        <v>30.6</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -828,19 +816,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>72.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="E14" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -859,13 +847,13 @@
         <v>18.7</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -886,47 +874,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1319,42 +1307,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1379,13 +1367,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>89.2</v>
+        <v>93.8</v>
       </c>
       <c r="G2" t="n">
-        <v>75.8</v>
+        <v>79.5</v>
       </c>
       <c r="H2" t="n">
-        <v>62.7</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="3">
@@ -1407,13 +1395,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>55.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>36</v>
+        <v>38.3</v>
       </c>
       <c r="H3" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="4">
@@ -1435,13 +1423,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>37.9</v>
       </c>
       <c r="G4" t="n">
-        <v>20.3</v>
+        <v>16.1</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="5">
@@ -1466,10 +1454,10 @@
         <v>62.8</v>
       </c>
       <c r="G5" t="n">
-        <v>14.1</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6">
@@ -1494,10 +1482,10 @@
         <v>26.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1494,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1516,16 +1504,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>61.4</v>
+        <v>71.7</v>
       </c>
       <c r="F7" t="n">
-        <v>29.3</v>
+        <v>49.4</v>
       </c>
       <c r="G7" t="n">
-        <v>10.4</v>
+        <v>28.3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1534,7 +1522,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1544,16 +1532,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>78.5</v>
+        <v>65.8</v>
       </c>
       <c r="F8" t="n">
-        <v>40.6</v>
+        <v>24.1</v>
       </c>
       <c r="G8" t="n">
-        <v>28.4</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>8.300000000000001</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -1562,7 +1550,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Florida St</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1572,16 +1560,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>27.4</v>
+        <v>52.7</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -1590,7 +1578,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>California</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1600,16 +1588,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>72.59999999999999</v>
+        <v>47.3</v>
       </c>
       <c r="F10" t="n">
-        <v>9.1</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -1618,26 +1606,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Florida St</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>63.3</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>14.3</v>
+        <v>23.2</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -1646,26 +1634,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>63.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>27.4</v>
+        <v>23.2</v>
       </c>
       <c r="F12" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -1690,7 +1678,7 @@
         <v>5.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="n">
         <v>0.2</v>
@@ -1737,19 +1725,19 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>36.4</v>
+        <v>28.6</v>
       </c>
       <c r="E15" t="n">
-        <v>11.2</v>
+        <v>5.2</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1765,19 +1753,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36.6</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>7.2</v>
+        <v>11.1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1795,42 +1783,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1855,13 +1843,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>81.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="n">
-        <v>61.1</v>
+        <v>60.8</v>
       </c>
       <c r="H2" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="3">
@@ -1883,13 +1871,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>82.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>51.4</v>
+        <v>47.8</v>
       </c>
       <c r="H3" t="n">
-        <v>26.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -1911,13 +1899,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>76.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>37.8</v>
+        <v>36.4</v>
       </c>
       <c r="H4" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="5">
@@ -1926,7 +1914,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1939,13 +1927,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>44.7</v>
+        <v>68.7</v>
       </c>
       <c r="G5" t="n">
-        <v>12.3</v>
+        <v>26.2</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="6">
@@ -1954,7 +1942,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1964,16 +1952,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>77.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>49.2</v>
+        <v>26.5</v>
       </c>
       <c r="G6" t="n">
-        <v>19.1</v>
+        <v>7.4</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -1982,7 +1970,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1992,16 +1980,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>52.8</v>
       </c>
       <c r="F7" t="n">
-        <v>17.9</v>
+        <v>14.4</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -2010,7 +1998,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2020,16 +2008,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>54.3</v>
+        <v>39.2</v>
       </c>
       <c r="F8" t="n">
-        <v>10.6</v>
+        <v>7.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -2038,7 +2026,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2048,16 +2036,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>37.2</v>
+        <v>64.8</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -2066,26 +2054,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>82.90000000000001</v>
+        <v>63.7</v>
       </c>
       <c r="E10" t="n">
-        <v>56.4</v>
+        <v>28.2</v>
       </c>
       <c r="F10" t="n">
-        <v>13.2</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -2094,26 +2082,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>71.3</v>
+        <v>80.7</v>
       </c>
       <c r="E11" t="n">
-        <v>37.6</v>
+        <v>55.4</v>
       </c>
       <c r="F11" t="n">
-        <v>6.2</v>
+        <v>14.9</v>
       </c>
       <c r="G11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -2129,16 +2117,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>51.5</v>
+        <v>31.8</v>
       </c>
       <c r="E12" t="n">
-        <v>18.5</v>
+        <v>11.3</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2157,16 +2145,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>41.4</v>
+        <v>52.3</v>
       </c>
       <c r="E13" t="n">
-        <v>7.1</v>
+        <v>13.7</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
@@ -2178,26 +2166,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Oklahoma St</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>58.6</v>
+        <v>47.7</v>
       </c>
       <c r="E14" t="n">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -2206,26 +2194,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oklahoma St</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>48.5</v>
+        <v>68.2</v>
       </c>
       <c r="E15" t="n">
-        <v>17.9</v>
+        <v>35.9</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -2241,13 +2229,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>28.7</v>
+        <v>19.4</v>
       </c>
       <c r="E16" t="n">
-        <v>8.1</v>
+        <v>5.3</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -2269,10 +2257,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>17.1</v>
+        <v>36.3</v>
       </c>
       <c r="E17" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2299,37 +2287,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2354,10 +2342,10 @@
         <v>87.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>70.5</v>
+        <v>69.5</v>
       </c>
       <c r="G2" t="n">
-        <v>43.5</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="3">
@@ -2379,10 +2367,10 @@
         <v>85.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>64.09999999999999</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>36.2</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="4">
@@ -2401,13 +2389,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74.3</v>
       </c>
       <c r="F4" t="n">
-        <v>25.1</v>
+        <v>27.2</v>
       </c>
       <c r="G4" t="n">
-        <v>9.699999999999999</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -2426,13 +2414,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>64.2</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>17.7</v>
+        <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="6">
@@ -2441,7 +2429,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2451,13 +2439,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>35.8</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>6.9</v>
+        <v>10.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -2466,23 +2454,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>55.1</v>
+        <v>43.5</v>
       </c>
       <c r="E7" t="n">
-        <v>14.9</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -2504,10 +2492,10 @@
         <v>8.5</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -2529,7 +2517,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
         <v>0.8</v>
@@ -2554,7 +2542,7 @@
         <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
@@ -2566,7 +2554,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2591,23 +2579,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>44.9</v>
+        <v>56.5</v>
       </c>
       <c r="E12" t="n">
-        <v>12.1</v>
+        <v>14.7</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -2625,47 +2613,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2693,13 +2681,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="H2" t="n">
         <v>49.6</v>
       </c>
       <c r="I2" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -2708,7 +2696,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2724,13 +2712,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>64.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>29.5</v>
+        <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>9.699999999999999</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="4">
@@ -2739,7 +2727,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2755,13 +2743,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>72.2</v>
+        <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>47.2</v>
+        <v>27.5</v>
       </c>
       <c r="I4" t="n">
-        <v>21.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5">
@@ -2786,13 +2774,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>58</v>
+        <v>60.4</v>
       </c>
       <c r="H5" t="n">
-        <v>25.8</v>
+        <v>26.8</v>
       </c>
       <c r="I5" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -2814,16 +2802,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>40.1</v>
+        <v>38.1</v>
       </c>
       <c r="H6" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -2845,16 +2833,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>23.9</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -2876,16 +2864,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>24.2</v>
+        <v>17.4</v>
       </c>
       <c r="H8" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -2894,7 +2882,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2907,16 +2895,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>50.8</v>
       </c>
       <c r="G9" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -2925,7 +2913,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2935,19 +2923,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>73.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="F10" t="n">
-        <v>32.3</v>
+        <v>43.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -2966,19 +2954,19 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>62.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>27.6</v>
+        <v>28.3</v>
       </c>
       <c r="G11" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -2987,7 +2975,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2997,19 +2985,19 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>65.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19</v>
+        <v>26.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -3018,7 +3006,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3028,16 +3016,16 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>43.8</v>
+        <v>56.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5.2</v>
+        <v>10.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3049,7 +3037,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3059,19 +3047,19 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>56.2</v>
+        <v>43.5</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6</v>
+        <v>4.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3090,10 +3078,10 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>34.9</v>
+        <v>29.6</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
         <v>0.5</v>
@@ -3118,22 +3106,22 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>68.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="F16" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="H16" t="n">
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -3149,16 +3137,16 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>57.1</v>
+        <v>59.8</v>
       </c>
       <c r="E17" t="n">
-        <v>18.4</v>
+        <v>14.5</v>
       </c>
       <c r="F17" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3180,13 +3168,13 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>42.9</v>
+        <v>40.2</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -3211,16 +3199,16 @@
         <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>31.1</v>
+        <v>28.1</v>
       </c>
       <c r="E19" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -3244,32 +3232,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3294,7 +3282,7 @@
         <v>62.3</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="3">
@@ -3310,13 +3298,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>96.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>77.2</v>
+        <v>71.8</v>
       </c>
       <c r="F3" t="n">
-        <v>56.8</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="4">
@@ -3335,10 +3323,10 @@
         <v>57.7</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9</v>
+        <v>14.8</v>
       </c>
       <c r="F4" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="5">
@@ -3360,7 +3348,7 @@
         <v>25.4</v>
       </c>
       <c r="F5" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6">
@@ -3382,7 +3370,7 @@
         <v>6.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -3401,10 +3389,10 @@
         <v>42.3</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -3413,20 +3401,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C Michigan</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>3.9</v>
+        <v>10.6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -3435,7 +3423,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3448,7 +3436,7 @@
         <v>5.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -3466,37 +3454,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3792,37 +3780,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3847,10 +3835,10 @@
         <v>81.2</v>
       </c>
       <c r="F2" t="n">
-        <v>59.8</v>
+        <v>60.4</v>
       </c>
       <c r="G2" t="n">
-        <v>38.2</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="3">
@@ -3869,13 +3857,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>64.3</v>
+        <v>68.3</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>39.6</v>
       </c>
       <c r="G3" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="4">
@@ -3894,13 +3882,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>67.8</v>
+        <v>57.4</v>
       </c>
       <c r="F4" t="n">
-        <v>32.5</v>
+        <v>27.9</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3909,7 +3897,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Grand Canyon</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3919,13 +3907,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>49.1</v>
+        <v>57.8</v>
       </c>
       <c r="F5" t="n">
-        <v>17.3</v>
+        <v>19.4</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -3934,23 +3922,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grand Canyon</t>
+          <t>Colorado St</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>99.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="E6" t="n">
-        <v>50.9</v>
+        <v>42.1</v>
       </c>
       <c r="F6" t="n">
-        <v>16.9</v>
+        <v>13.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="7">
@@ -3959,23 +3947,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>87.90000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>30.9</v>
+        <v>41.5</v>
       </c>
       <c r="F7" t="n">
-        <v>10.4</v>
+        <v>19.2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -3984,23 +3972,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>77.2</v>
+        <v>74.3</v>
       </c>
       <c r="E8" t="n">
-        <v>32</v>
+        <v>27.5</v>
       </c>
       <c r="F8" t="n">
-        <v>16.2</v>
+        <v>12.3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9">
@@ -4022,10 +4010,10 @@
         <v>7.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -4047,10 +4035,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -4066,10 +4054,10 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>22.8</v>
+        <v>25.7</v>
       </c>
       <c r="E11" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
@@ -4091,10 +4079,10 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>12.1</v>
+        <v>10.4</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="F12" t="n">
         <v>0.1</v>
@@ -4116,7 +4104,7 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4143,42 +4131,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4203,13 +4191,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>74.3</v>
+        <v>78.5</v>
       </c>
       <c r="G2" t="n">
-        <v>60.5</v>
+        <v>56.7</v>
       </c>
       <c r="H2" t="n">
-        <v>37.9</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="3">
@@ -4231,13 +4219,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>37.6</v>
+        <v>36.2</v>
       </c>
       <c r="H3" t="n">
-        <v>20.2</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="4">
@@ -4259,13 +4247,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>50.8</v>
+        <v>51.6</v>
       </c>
       <c r="G4" t="n">
-        <v>24.8</v>
+        <v>27.3</v>
       </c>
       <c r="H4" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="5">
@@ -4274,7 +4262,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4287,13 +4275,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>38.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>6.7</v>
+        <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="6">
@@ -4302,7 +4290,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4312,16 +4300,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>73.09999999999999</v>
+        <v>56.3</v>
       </c>
       <c r="F6" t="n">
-        <v>49.8</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>15.1</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
@@ -4330,7 +4318,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4343,13 +4331,13 @@
         <v>65.7</v>
       </c>
       <c r="F7" t="n">
-        <v>34.9</v>
+        <v>34.3</v>
       </c>
       <c r="G7" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="H7" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8">
@@ -4358,7 +4346,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4368,13 +4356,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>53.6</v>
+        <v>55.5</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>19.9</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -4386,7 +4374,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4396,16 +4384,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>68.2</v>
+        <v>53.4</v>
       </c>
       <c r="F9" t="n">
-        <v>19.8</v>
+        <v>12.8</v>
       </c>
       <c r="G9" t="n">
-        <v>12.9</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>6.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4414,26 +4402,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>43.1</v>
       </c>
       <c r="F10" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -4442,26 +4430,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>72.5</v>
+        <v>64.3</v>
       </c>
       <c r="E11" t="n">
-        <v>37.9</v>
+        <v>33.4</v>
       </c>
       <c r="F11" t="n">
-        <v>13.5</v>
+        <v>10.4</v>
       </c>
       <c r="G11" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
@@ -4483,13 +4471,13 @@
         <v>28.8</v>
       </c>
       <c r="F12" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -4498,26 +4486,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mississippi St</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>36.4</v>
+        <v>64.5</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
@@ -4526,26 +4514,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Mississippi St</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>63.6</v>
+        <v>35.5</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>12.7</v>
       </c>
       <c r="F14" t="n">
-        <v>9.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4589,16 +4577,16 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>27.5</v>
+        <v>35.7</v>
       </c>
       <c r="E16" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
@@ -4617,10 +4605,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="F17" t="n">
         <v>0.1</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -26,13 +26,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -51,12 +54,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,42 +438,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -486,13 +498,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>76.5</v>
+        <v>77.7</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>56.9</v>
       </c>
       <c r="H2" t="n">
-        <v>35.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="3">
@@ -517,10 +529,10 @@
         <v>81</v>
       </c>
       <c r="G3" t="n">
-        <v>62.7</v>
+        <v>62.5</v>
       </c>
       <c r="H3" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +557,10 @@
         <v>48.4</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -570,10 +582,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>70.5</v>
+        <v>69.7</v>
       </c>
       <c r="G5" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="H5" t="n">
         <v>12</v>
@@ -595,16 +607,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>68.8</v>
+        <v>68.3</v>
       </c>
       <c r="F6" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -623,16 +635,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="G7" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +672,7 @@
         <v>5.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -669,7 +681,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G Washington</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -679,16 +691,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>26.5</v>
       </c>
       <c r="F9" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>11.2</v>
+        <v>0.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -697,7 +709,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>G Washington</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -707,16 +719,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>73.5</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>20.1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="11">
@@ -741,7 +753,7 @@
         <v>9.1</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
         <v>0.8</v>
@@ -788,13 +800,13 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>30.6</v>
+        <v>27.6</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
         <v>0.1</v>
@@ -816,19 +828,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>69.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="F14" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -847,13 +859,13 @@
         <v>18.7</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -874,47 +886,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1307,42 +1319,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1367,13 +1379,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>93.8</v>
+        <v>89.2</v>
       </c>
       <c r="G2" t="n">
-        <v>79.5</v>
+        <v>75.8</v>
       </c>
       <c r="H2" t="n">
-        <v>65.3</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="3">
@@ -1395,13 +1407,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>67.90000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="G3" t="n">
-        <v>38.3</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="4">
@@ -1423,13 +1435,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>37.9</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>16.1</v>
+        <v>20.3</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
@@ -1454,10 +1466,10 @@
         <v>62.8</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>14.1</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
@@ -1482,10 +1494,10 @@
         <v>26.9</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -1494,7 +1506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>NC State</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1504,16 +1516,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>71.7</v>
+        <v>61.4</v>
       </c>
       <c r="F7" t="n">
-        <v>49.4</v>
+        <v>29.3</v>
       </c>
       <c r="G7" t="n">
-        <v>28.3</v>
+        <v>10.4</v>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -1522,7 +1534,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NC State</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1532,16 +1544,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>65.8</v>
+        <v>78.5</v>
       </c>
       <c r="F8" t="n">
-        <v>24.1</v>
+        <v>40.6</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>28.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1550,7 +1562,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Florida St</t>
+          <t>California</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1560,16 +1572,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>52.7</v>
+        <v>27.4</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1578,7 +1590,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>SMU</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1588,16 +1600,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>47.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>9.1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -1606,26 +1618,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Florida St</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="E11" t="n">
-        <v>23.2</v>
+        <v>14.3</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1634,26 +1646,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SMU</t>
+          <t>Stanford</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>71.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="E12" t="n">
-        <v>23.2</v>
+        <v>27.4</v>
       </c>
       <c r="F12" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -1678,7 +1690,7 @@
         <v>5.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="n">
         <v>0.2</v>
@@ -1725,19 +1737,19 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>28.6</v>
+        <v>36.4</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2</v>
+        <v>11.2</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -1753,19 +1765,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="E16" t="n">
-        <v>11.1</v>
+        <v>7.2</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1783,42 +1795,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1843,13 +1855,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>60.8</v>
+        <v>61.1</v>
       </c>
       <c r="H2" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="3">
@@ -1871,13 +1883,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>76.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="G3" t="n">
-        <v>47.8</v>
+        <v>51.4</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="4">
@@ -1899,13 +1911,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>74.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="G4" t="n">
-        <v>36.4</v>
+        <v>37.8</v>
       </c>
       <c r="H4" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="5">
@@ -1914,7 +1926,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1927,13 +1939,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>68.7</v>
+        <v>44.7</v>
       </c>
       <c r="G5" t="n">
-        <v>26.2</v>
+        <v>12.3</v>
       </c>
       <c r="H5" t="n">
-        <v>13.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6">
@@ -1942,7 +1954,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1952,16 +1964,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>72.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="F6" t="n">
-        <v>26.5</v>
+        <v>49.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>19.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1970,7 +1982,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1980,16 +1992,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>52.8</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>14.4</v>
+        <v>17.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -1998,7 +2010,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2008,16 +2020,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>39.2</v>
+        <v>54.3</v>
       </c>
       <c r="F8" t="n">
-        <v>7.9</v>
+        <v>10.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -2026,7 +2038,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2036,16 +2048,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>64.8</v>
+        <v>37.2</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10">
@@ -2054,26 +2066,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>63.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>28.2</v>
+        <v>56.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>13.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -2082,26 +2094,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>80.7</v>
+        <v>71.3</v>
       </c>
       <c r="E11" t="n">
-        <v>55.4</v>
+        <v>37.6</v>
       </c>
       <c r="F11" t="n">
-        <v>14.9</v>
+        <v>6.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -2117,16 +2129,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>31.8</v>
+        <v>51.5</v>
       </c>
       <c r="E12" t="n">
-        <v>11.3</v>
+        <v>18.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2145,16 +2157,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>52.3</v>
+        <v>41.4</v>
       </c>
       <c r="E13" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
@@ -2166,26 +2178,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oklahoma St</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>47.7</v>
+        <v>58.6</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -2194,26 +2206,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Oklahoma St</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>68.2</v>
+        <v>48.5</v>
       </c>
       <c r="E15" t="n">
-        <v>35.9</v>
+        <v>17.9</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -2229,13 +2241,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>19.4</v>
+        <v>28.7</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3</v>
+        <v>8.1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -2257,10 +2269,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>36.3</v>
+        <v>17.1</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="F17" t="n">
         <v>0.4</v>
@@ -2287,37 +2299,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2342,10 +2354,10 @@
         <v>87.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="G2" t="n">
-        <v>42.8</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="3">
@@ -2367,10 +2379,10 @@
         <v>85.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>35.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="4">
@@ -2389,13 +2401,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>74.3</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>27.2</v>
+        <v>25.1</v>
       </c>
       <c r="G4" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2414,13 +2426,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>64.2</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>17.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
@@ -2429,7 +2441,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2439,13 +2451,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>35.8</v>
       </c>
       <c r="F6" t="n">
-        <v>10.2</v>
+        <v>6.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -2454,23 +2466,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5</v>
+        <v>55.1</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>14.9</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -2492,10 +2504,10 @@
         <v>8.5</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -2517,7 +2529,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
         <v>0.8</v>
@@ -2542,7 +2554,7 @@
         <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
@@ -2554,7 +2566,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2579,23 +2591,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>56.5</v>
+        <v>44.9</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7</v>
+        <v>12.1</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2613,47 +2625,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2681,13 +2693,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>49.6</v>
       </c>
       <c r="I2" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="3">
@@ -2696,7 +2708,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2712,13 +2724,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>73.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="H3" t="n">
-        <v>48</v>
+        <v>29.5</v>
       </c>
       <c r="I3" t="n">
-        <v>21.8</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2727,7 +2739,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2743,13 +2755,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>72.2</v>
       </c>
       <c r="H4" t="n">
-        <v>27.5</v>
+        <v>47.2</v>
       </c>
       <c r="I4" t="n">
-        <v>8.6</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="5">
@@ -2774,13 +2786,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="H5" t="n">
-        <v>26.8</v>
+        <v>25.8</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="6">
@@ -2802,16 +2814,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>84.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G6" t="n">
-        <v>38.1</v>
+        <v>40.1</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>18.9</v>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="7">
@@ -2833,16 +2845,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>69.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>23.9</v>
       </c>
       <c r="H7" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -2864,16 +2876,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
+        <v>24.2</v>
       </c>
       <c r="H8" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -2882,7 +2894,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2895,16 +2907,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>50.8</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>9.699999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="10">
@@ -2913,7 +2925,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2923,19 +2935,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>78.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>43.7</v>
+        <v>32.3</v>
       </c>
       <c r="G10" t="n">
-        <v>8.699999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -2954,19 +2966,19 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>64.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="F11" t="n">
-        <v>28.3</v>
+        <v>27.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -2975,7 +2987,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2985,19 +2997,19 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>70.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>26.5</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -3006,7 +3018,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3016,16 +3028,16 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>56.5</v>
+        <v>43.8</v>
       </c>
       <c r="F13" t="n">
-        <v>10.9</v>
+        <v>5.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3037,7 +3049,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3047,19 +3059,19 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>43.5</v>
+        <v>56.2</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7</v>
+        <v>10.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3078,10 +3090,10 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>29.6</v>
+        <v>34.9</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0.5</v>
@@ -3106,22 +3118,22 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>71.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="F16" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="H16" t="n">
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3137,16 +3149,16 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>59.8</v>
+        <v>57.1</v>
       </c>
       <c r="E17" t="n">
-        <v>14.5</v>
+        <v>18.4</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3168,13 +3180,13 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>40.2</v>
+        <v>42.9</v>
       </c>
       <c r="E18" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -3199,16 +3211,16 @@
         <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>28.1</v>
+        <v>31.1</v>
       </c>
       <c r="E19" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -3232,32 +3244,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3282,7 +3294,7 @@
         <v>62.3</v>
       </c>
       <c r="F2" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -3298,13 +3310,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>89.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>71.8</v>
+        <v>77.2</v>
       </c>
       <c r="F3" t="n">
-        <v>52.8</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="4">
@@ -3323,10 +3335,10 @@
         <v>57.7</v>
       </c>
       <c r="E4" t="n">
-        <v>14.8</v>
+        <v>12.9</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="5">
@@ -3348,7 +3360,7 @@
         <v>25.4</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
@@ -3370,7 +3382,7 @@
         <v>6.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
@@ -3389,10 +3401,10 @@
         <v>42.3</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -3401,20 +3413,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>C Michigan</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>10.6</v>
+        <v>3.9</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -3423,7 +3435,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Buffalo</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3436,7 +3448,7 @@
         <v>5.9</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3454,37 +3466,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3780,37 +3792,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3835,10 +3847,10 @@
         <v>81.2</v>
       </c>
       <c r="F2" t="n">
-        <v>60.4</v>
+        <v>59.8</v>
       </c>
       <c r="G2" t="n">
-        <v>38.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -3857,13 +3869,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.3</v>
+        <v>64.3</v>
       </c>
       <c r="F3" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4">
@@ -3882,13 +3894,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>57.4</v>
+        <v>67.8</v>
       </c>
       <c r="F4" t="n">
-        <v>27.9</v>
+        <v>32.5</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -3897,7 +3909,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grand Canyon</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3907,13 +3919,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>57.8</v>
+        <v>49.1</v>
       </c>
       <c r="F5" t="n">
-        <v>19.4</v>
+        <v>17.3</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6">
@@ -3922,23 +3934,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Grand Canyon</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>42.1</v>
+        <v>50.9</v>
       </c>
       <c r="F6" t="n">
-        <v>13.2</v>
+        <v>16.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7">
@@ -3947,23 +3959,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Colorado St</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>89.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>41.5</v>
+        <v>30.9</v>
       </c>
       <c r="F7" t="n">
-        <v>19.2</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -3972,23 +3984,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>74.3</v>
+        <v>77.2</v>
       </c>
       <c r="E8" t="n">
-        <v>27.5</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>12.3</v>
+        <v>16.2</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9">
@@ -4010,10 +4022,10 @@
         <v>7.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -4035,10 +4047,10 @@
         <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -4054,10 +4066,10 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>22.8</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
@@ -4079,10 +4091,10 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>12.1</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
         <v>0.1</v>
@@ -4104,7 +4116,7 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -4131,42 +4143,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4191,13 +4203,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>78.5</v>
+        <v>74.3</v>
       </c>
       <c r="G2" t="n">
-        <v>56.7</v>
+        <v>60.5</v>
       </c>
       <c r="H2" t="n">
-        <v>35.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="3">
@@ -4219,13 +4231,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="G3" t="n">
-        <v>36.2</v>
+        <v>37.6</v>
       </c>
       <c r="H3" t="n">
-        <v>18.9</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="4">
@@ -4247,13 +4259,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>51.6</v>
+        <v>50.8</v>
       </c>
       <c r="G4" t="n">
-        <v>27.3</v>
+        <v>24.8</v>
       </c>
       <c r="H4" t="n">
-        <v>11.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="5">
@@ -4262,7 +4274,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4275,13 +4287,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>76.40000000000001</v>
+        <v>38.4</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
+        <v>6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>15.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
@@ -4290,7 +4302,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4300,16 +4312,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>56.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>49.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>15.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -4318,7 +4330,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4331,13 +4343,13 @@
         <v>65.7</v>
       </c>
       <c r="F7" t="n">
-        <v>34.3</v>
+        <v>34.9</v>
       </c>
       <c r="G7" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="H7" t="n">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8">
@@ -4346,7 +4358,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4356,13 +4368,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>55.5</v>
+        <v>53.6</v>
       </c>
       <c r="F8" t="n">
-        <v>19.9</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
@@ -4374,7 +4386,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4384,16 +4396,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>53.4</v>
+        <v>68.2</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>19.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>12.9</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="10">
@@ -4402,26 +4414,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>81.5</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>43.1</v>
+        <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>8.699999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4430,26 +4442,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>72.5</v>
       </c>
       <c r="E11" t="n">
-        <v>33.4</v>
+        <v>37.9</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>13.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4471,13 +4483,13 @@
         <v>28.8</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="G12" t="n">
         <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -4486,26 +4498,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Mississippi St</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>64.5</v>
+        <v>36.4</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>6.9</v>
       </c>
       <c r="F13" t="n">
-        <v>7.8</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4514,26 +4526,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mississippi St</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>35.5</v>
+        <v>63.6</v>
       </c>
       <c r="E14" t="n">
-        <v>12.7</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>1.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -4577,16 +4589,16 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35.7</v>
+        <v>27.5</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
@@ -4605,10 +4617,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="n">
         <v>0.1</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -945,10 +945,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="I2" t="n">
-        <v>65.09999999999999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -976,7 +976,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>26.2</v>
@@ -1004,13 +1004,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>84.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="H4" t="n">
-        <v>31.3</v>
+        <v>31.1</v>
       </c>
       <c r="I4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1035,7 +1035,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>39.2</v>
+        <v>39.7</v>
       </c>
       <c r="H5" t="n">
         <v>0.7</v>
@@ -1063,13 +1063,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>68.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>43.9</v>
+        <v>43.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="I6" t="n">
         <v>0.3</v>
@@ -1097,7 +1097,7 @@
         <v>48.7</v>
       </c>
       <c r="G7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H7" t="n">
         <v>0.6</v>
@@ -1122,16 +1122,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>62.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>34.8</v>
+        <v>46.3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1153,13 +1153,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>73.3</v>
+        <v>72.7</v>
       </c>
       <c r="F9" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="H9" t="n">
         <v>0.6</v>
@@ -1181,19 +1181,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>16.1</v>
+        <v>27.3</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1212,19 +1212,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>77.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1243,16 +1243,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>22.4</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8</v>
+        <v>17.9</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1274,16 +1274,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2681,13 +2681,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>81.2</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>49.6</v>
+        <v>45.8</v>
       </c>
       <c r="I2" t="n">
-        <v>33</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="3">
@@ -2715,10 +2715,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I3" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="4">
@@ -2746,10 +2746,10 @@
         <v>61</v>
       </c>
       <c r="H4" t="n">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="I4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5">
@@ -2777,10 +2777,10 @@
         <v>60.4</v>
       </c>
       <c r="H5" t="n">
-        <v>26.8</v>
+        <v>29.4</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>18.1</v>
       </c>
     </row>
     <row r="6">
@@ -2808,7 +2808,7 @@
         <v>38.1</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="I6" t="n">
         <v>11.2</v>
@@ -2873,7 +2873,7 @@
         <v>7.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -2895,7 +2895,7 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="G9" t="n">
         <v>9.699999999999999</v>
@@ -2923,19 +2923,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>78.3</v>
+        <v>79.8</v>
       </c>
       <c r="F10" t="n">
-        <v>43.7</v>
+        <v>44.5</v>
       </c>
       <c r="G10" t="n">
-        <v>8.699999999999999</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -2966,7 +2966,7 @@
         <v>2.7</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -2994,10 +2994,10 @@
         <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -3171,10 +3171,10 @@
         <v>40.2</v>
       </c>
       <c r="E18" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -3506,13 +3506,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>76.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="F2" t="n">
-        <v>54.7</v>
+        <v>62.5</v>
       </c>
       <c r="G2" t="n">
-        <v>38.7</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="3">
@@ -3531,13 +3531,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.59999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="F3" t="n">
-        <v>31.4</v>
+        <v>29.1</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="4">
@@ -3556,13 +3556,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>12.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -3584,10 +3584,10 @@
         <v>49.9</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -3609,10 +3609,10 @@
         <v>50.1</v>
       </c>
       <c r="F6" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="7">
@@ -3628,16 +3628,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>90.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>48.9</v>
+        <v>54</v>
       </c>
       <c r="F7" t="n">
-        <v>29.8</v>
+        <v>33.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -3653,16 +3653,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>22.8</v>
+        <v>35.8</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>10.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -3678,16 +3678,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>69.5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3703,16 +3703,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>30.5</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>3.9</v>
+        <v>12.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -3728,16 +3728,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -3753,13 +3753,13 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -9,14 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlantic 10" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big 12" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big East" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big Ten" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mid-American" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missouri Valley" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mountain West" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCC" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="American Athletic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big 12" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big East" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big South" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Big Ten" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAA" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conference USA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mid-American" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missouri Valley" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mountain West" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Patriot" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEC" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Southern" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Southland" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WCC" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,6 +877,2078 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_QF</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Miami OH</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Akron</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>52.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bowling Green</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_R1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_QF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Belmont</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bradley</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Illinois St</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>46</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Murray St</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IL Chicago</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Northern Iowa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>54</v>
+      </c>
+      <c r="F7" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S Illinois</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Drake</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Indiana St</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Evansville</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_R1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_QF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Utah St</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>San Diego St</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Grand Canyon</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Colorado St</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>97</v>
+      </c>
+      <c r="E6" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Boise St</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fresno St</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>San Jose St</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Air Force</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>63.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lehigh</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Colgate</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>22.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Boston Univ</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_R1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_R2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_QF</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>29</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Vanderbilt</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Texas A&amp;M</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="F12" t="n">
+        <v>13</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>31</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mississippi St</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_R1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_QF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ETSU</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mercer</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>52</v>
+      </c>
+      <c r="G3" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Wofford</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Samford</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>W Carolina</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Furman</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UNC Greensboro</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chattanooga</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Citadel</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VMI</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_R1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_QF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_SF</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pct_Final</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_Champion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SF Austin</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>McNeese St</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>UTRGV</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TAM C. Christi</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>New Orleans</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nicholls St</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Houston Chr</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Northwestern LA</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1779,7 +3858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1830,7 +3909,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>South Florida</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1843,13 +3922,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>60.8</v>
+        <v>79.3</v>
       </c>
       <c r="H2" t="n">
-        <v>39.9</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="3">
@@ -1858,7 +3937,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1871,13 +3950,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>76.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>47.8</v>
+        <v>66.8</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="4">
@@ -1886,7 +3965,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1899,13 +3978,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>74.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G4" t="n">
-        <v>36.4</v>
+        <v>25.9</v>
       </c>
       <c r="H4" t="n">
-        <v>13.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1914,7 +3993,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>UAB</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1927,13 +4006,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>68.7</v>
+        <v>53.2</v>
       </c>
       <c r="G5" t="n">
-        <v>26.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>13.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -1942,7 +4021,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>FL Atlantic</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1952,16 +4031,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>72.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>26.5</v>
+        <v>37.1</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -1970,7 +4049,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TCU</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1980,16 +4059,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>52.8</v>
+        <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>14.4</v>
+        <v>5.9</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -1998,23 +4077,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>47.9</v>
       </c>
       <c r="E8" t="n">
-        <v>39.2</v>
+        <v>30.5</v>
       </c>
       <c r="F8" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>0.6</v>
@@ -2026,26 +4105,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>Tulane</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>43.7</v>
       </c>
       <c r="E9" t="n">
-        <v>64.8</v>
+        <v>12.6</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -2054,26 +4133,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>Temple</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>63.7</v>
+        <v>56.3</v>
       </c>
       <c r="E10" t="n">
-        <v>28.2</v>
+        <v>16.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -2082,194 +4161,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BYU</t>
+          <t>Memphis</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>80.7</v>
+        <v>52.1</v>
       </c>
       <c r="E11" t="n">
-        <v>55.4</v>
+        <v>37.5</v>
       </c>
       <c r="F11" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Colorado</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Arizona St</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="E13" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Oklahoma St</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="E14" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Baylor</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>9</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Kansas St</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Utah</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -2283,7 +4194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2304,20 +4215,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>pct_R2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2329,7 +4245,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2339,13 +4255,16 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>87.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>69.5</v>
+        <v>84.2</v>
       </c>
       <c r="G2" t="n">
-        <v>42.8</v>
+        <v>60.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.9</v>
       </c>
     </row>
     <row r="3">
@@ -2354,7 +4273,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2364,13 +4283,16 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>85.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>35.8</v>
+        <v>47.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2379,7 +4301,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villanova</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2389,13 +4311,16 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>74.3</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>27.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>10.7</v>
+        <v>36.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>13.9</v>
       </c>
     </row>
     <row r="5">
@@ -2404,7 +4329,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Seton Hall</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2414,13 +4339,16 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>68.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>26.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.9</v>
       </c>
     </row>
     <row r="6">
@@ -2429,7 +4357,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2439,13 +4367,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>10.2</v>
+        <v>26.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>7.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2454,23 +4385,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DePaul</t>
+          <t>TCU</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>52.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>14.4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -2479,23 +4413,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>56.3</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>8.5</v>
+        <v>39.2</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -2504,23 +4441,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>56.4</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>8.300000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -2529,23 +4469,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>43.6</v>
+        <v>63.7</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3</v>
+        <v>28.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -2554,23 +4497,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>BYU</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>43.7</v>
+        <v>80.7</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>55.4</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>14.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2579,23 +4525,166 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Georgetown</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>56.5</v>
+        <v>31.8</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7</v>
+        <v>11.3</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="G12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Arizona St</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Oklahoma St</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Baylor</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kansas St</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2609,7 +4698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2630,30 +4719,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>pct_R2</t>
+          <t>pct_QF</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pct_R3</t>
+          <t>pct_SF</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>pct_QF</t>
+          <t>pct_Final</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>pct_SF</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pct_Final</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2665,7 +4744,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Michigan</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2675,19 +4754,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>100</v>
+        <v>69.5</v>
       </c>
       <c r="G2" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31.9</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="3">
@@ -2696,7 +4769,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Michigan St</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -2706,19 +4779,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="H3" t="n">
-        <v>49</v>
-      </c>
-      <c r="I3" t="n">
-        <v>21.3</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="4">
@@ -2727,7 +4794,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Villanova</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2737,19 +4804,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>74.3</v>
       </c>
       <c r="F4" t="n">
-        <v>100</v>
+        <v>27.2</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
-      </c>
-      <c r="H4" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="5">
@@ -2758,7 +4819,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Seton Hall</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2768,19 +4829,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>15.5</v>
       </c>
       <c r="G5" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>18.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="6">
@@ -2789,7 +4844,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Creighton</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2799,19 +4854,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>84.40000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="G6" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>11.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -2820,29 +4869,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>DePaul</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>100</v>
+        <v>43.5</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
-        <v>69.40000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
-      </c>
-      <c r="H7" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -2851,29 +4894,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>56.3</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>8.5</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -2882,29 +4919,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ohio St</t>
+          <t>Butler</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>56.4</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>50.3</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -2913,29 +4944,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>43.6</v>
       </c>
       <c r="E10" t="n">
-        <v>79.8</v>
+        <v>4.3</v>
       </c>
       <c r="F10" t="n">
-        <v>44.5</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
@@ -2944,28 +4969,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>43.7</v>
       </c>
       <c r="E11" t="n">
-        <v>64.59999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="F11" t="n">
-        <v>28.3</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -2975,246 +4994,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Georgetown</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>56.5</v>
       </c>
       <c r="E12" t="n">
-        <v>70.40000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="F12" t="n">
-        <v>26.5</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>USC</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="n">
-        <v>100</v>
-      </c>
-      <c r="E13" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="n">
-        <v>100</v>
-      </c>
-      <c r="E14" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="F14" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Rutgers</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="n">
-        <v>100</v>
-      </c>
-      <c r="E15" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="F15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Northwestern</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="E16" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>100</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Penn St</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3244,20 +5040,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>pct_R1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3269,20 +5070,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Miami OH</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>62.3</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>27.5</v>
+        <v>89.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>76.7</v>
       </c>
     </row>
     <row r="3">
@@ -3291,20 +5095,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Winthrop</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>89.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>71.8</v>
+        <v>73.8</v>
       </c>
       <c r="F3" t="n">
-        <v>52.8</v>
+        <v>57.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.9</v>
       </c>
     </row>
     <row r="4">
@@ -3313,20 +5120,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Radford</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>14.8</v>
+        <v>59.3</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>19.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -3335,20 +5145,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Toledo</t>
+          <t>UNC Asheville</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>71.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>25.4</v>
+        <v>51.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3</v>
+        <v>5.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
@@ -3357,20 +5170,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Longwood</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>28.1</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
+        <v>48.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>4.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -3379,20 +5195,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bowling Green</t>
+          <t>Presbyterian</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>42.3</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>40.7</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>9.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -3401,20 +5220,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Buffalo</t>
+          <t>Charleston So</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>10.6</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4</v>
+        <v>26.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>13.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -3423,20 +5245,48 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>SC Upstate</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>15.4</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Gardner Webb</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3450,7 +5300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3471,20 +5321,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>pct_R2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_R3</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3496,7 +5356,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Belmont</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3506,13 +5366,19 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>87.8</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>44.3</v>
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>31.9</v>
       </c>
     </row>
     <row r="3">
@@ -3521,7 +5387,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bradley</t>
+          <t>Michigan St</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3531,13 +5397,19 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>64.2</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>29.1</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7</v>
+        <v>73.40000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>49</v>
+      </c>
+      <c r="I3" t="n">
+        <v>21.3</v>
       </c>
     </row>
     <row r="4">
@@ -3546,7 +5418,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Illinois St</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3556,13 +5428,19 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>10.7</v>
+        <v>61</v>
+      </c>
+      <c r="H4" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5">
@@ -3571,7 +5449,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Murray St</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3581,13 +5459,19 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>49.9</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>17.2</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>60.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18.1</v>
       </c>
     </row>
     <row r="6">
@@ -3596,7 +5480,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IL Chicago</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -3606,13 +5490,19 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>50.1</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>16.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>7.9</v>
+        <v>38.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -3621,7 +5511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Northern Iowa</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3631,13 +5521,19 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>33.1</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>31</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -3646,7 +5542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -3656,13 +5552,19 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>35.8</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>10.8</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>17.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -3671,23 +5573,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S Illinois</t>
+          <t>Ohio St</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>50.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -3696,7 +5604,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3706,13 +5614,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>12.2</v>
+        <v>79.8</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>44.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -3721,23 +5635,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Indiana St</t>
+          <t>Indiana</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>7.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
@@ -3746,22 +5666,245 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Evansville</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="n">
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rutgers</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Northwestern</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D17" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>100</v>
+      </c>
+      <c r="D18" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Penn St</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3776,7 +5919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3797,20 +5940,25 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>pct_R2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3822,7 +5970,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Utah St</t>
+          <t>UNC Wilmington</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3832,13 +5980,16 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>81.2</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>60.4</v>
+        <v>82.2</v>
       </c>
       <c r="G2" t="n">
-        <v>38.7</v>
+        <v>64.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -3847,7 +5998,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Col Charleston</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3857,13 +6008,16 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.3</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>39.6</v>
+        <v>59.8</v>
       </c>
       <c r="G3" t="n">
-        <v>20.1</v>
+        <v>26</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12.1</v>
       </c>
     </row>
     <row r="4">
@@ -3872,7 +6026,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Diego St</t>
+          <t>Hofstra</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3882,13 +6036,16 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>57.4</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>27.9</v>
+        <v>69.8</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>46.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>28.6</v>
       </c>
     </row>
     <row r="5">
@@ -3897,7 +6054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grand Canyon</t>
+          <t>Monmouth NJ</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3907,13 +6064,16 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>57.8</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>19.4</v>
+        <v>63.3</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1</v>
+        <v>20.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.6</v>
       </c>
     </row>
     <row r="6">
@@ -3922,23 +6082,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Drexel</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>42.1</v>
+        <v>71.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13.2</v>
+        <v>29.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -3947,23 +6110,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>William &amp; Mary</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>89.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>41.5</v>
+        <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>19.2</v>
+        <v>20.3</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="8">
@@ -3972,23 +6138,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Towson</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
         <v>74.3</v>
       </c>
-      <c r="E8" t="n">
-        <v>27.5</v>
-      </c>
       <c r="F8" t="n">
-        <v>12.3</v>
+        <v>35.2</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>13.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.8</v>
       </c>
     </row>
     <row r="9">
@@ -3997,23 +6166,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNLV</t>
+          <t>Stony Brook</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>43.4</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>7.8</v>
+        <v>39.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -4022,23 +6194,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>56.6</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>60.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>11.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -4047,22 +6222,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fresno St</t>
+          <t>Hampton</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
         <v>25.7</v>
       </c>
-      <c r="E11" t="n">
-        <v>4.2</v>
-      </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -4072,23 +6250,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>San Jose St</t>
+          <t>Elon</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1</v>
+        <v>36.4</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1</v>
+        <v>9.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3.1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -4097,23 +6278,54 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Air Force</t>
+          <t>NC A&amp;T</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>52.3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>15.1</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Northeastern</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4127,7 +6339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4148,25 +6360,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>pct_R2</t>
+          <t>pct_QF</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pct_QF</t>
+          <t>pct_SF</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>pct_SF</t>
+          <t>pct_Final</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>pct_Final</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4178,7 +6385,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Liberty</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4188,16 +6395,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="F2" t="n">
-        <v>78.5</v>
+        <v>49.6</v>
       </c>
       <c r="G2" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>35.7</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="3">
@@ -4206,7 +6410,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Sam Houston St</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4216,16 +6420,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>100</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>43.1</v>
       </c>
       <c r="G3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>18.9</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="4">
@@ -4234,7 +6435,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>WKU</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4244,16 +6445,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>72.3</v>
       </c>
       <c r="F4" t="n">
-        <v>51.6</v>
+        <v>36.4</v>
       </c>
       <c r="G4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>11.7</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="5">
@@ -4262,7 +6460,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>MTSU</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4272,16 +6470,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>48.5</v>
       </c>
       <c r="F5" t="n">
-        <v>76.40000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
-      </c>
-      <c r="H5" t="n">
-        <v>15.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6">
@@ -4290,7 +6485,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Kennesaw</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4300,16 +6495,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>56.3</v>
+        <v>51.5</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>21.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -4318,7 +6510,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4328,16 +6520,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>65.7</v>
+        <v>27.7</v>
       </c>
       <c r="F7" t="n">
-        <v>34.3</v>
+        <v>7.3</v>
       </c>
       <c r="G7" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -4346,26 +6535,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Jacksonville St</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>100</v>
+        <v>43.4</v>
       </c>
       <c r="E8" t="n">
-        <v>55.5</v>
+        <v>11.3</v>
       </c>
       <c r="F8" t="n">
-        <v>19.9</v>
+        <v>4.2</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -4374,26 +6560,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Missouri St</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>53.4</v>
+        <v>13.4</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -4402,26 +6585,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Florida Intl</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>81.5</v>
+        <v>51.9</v>
       </c>
       <c r="E10" t="n">
-        <v>43.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>8.699999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -4430,194 +6610,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>New Mexico St</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>56.6</v>
       </c>
       <c r="E11" t="n">
-        <v>33.4</v>
+        <v>20.4</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Auburn</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="F12" t="n">
-        <v>13</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H12" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>31</v>
-      </c>
-      <c r="F13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Mississippi St</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>100</v>
-      </c>
-      <c r="D14" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="E14" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Mississippi</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>100</v>
-      </c>
-      <c r="D15" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LSU</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="E16" t="n">
-        <v>11</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>100</v>
-      </c>
-      <c r="D17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="E17" t="n">
         <v>3.5</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -1155,13 +1155,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>87.8</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>62.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>44.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1186,7 +1186,7 @@
         <v>29.1</v>
       </c>
       <c r="G3" t="n">
-        <v>11.7</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="4">
@@ -1211,7 +1211,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>10.7</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="5">
@@ -1230,13 +1230,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>49.9</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1255,13 +1255,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>50.1</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>16.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>7.9</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="7">
@@ -1286,7 +1286,7 @@
         <v>33.1</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="8">
@@ -1311,7 +1311,7 @@
         <v>10.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -1355,13 +1355,13 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>12.2</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>30.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -2453,13 +2453,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>87.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>60.8</v>
+        <v>65.2</v>
       </c>
       <c r="G2" t="n">
-        <v>38.5</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="3">
@@ -2484,7 +2484,7 @@
         <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>26.5</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="4">
@@ -2509,7 +2509,7 @@
         <v>13.9</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
@@ -2531,10 +2531,10 @@
         <v>55.2</v>
       </c>
       <c r="F5" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="G5" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2556,10 +2556,10 @@
         <v>44.8</v>
       </c>
       <c r="F6" t="n">
-        <v>16.7</v>
+        <v>15.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="7">
@@ -2584,7 +2584,7 @@
         <v>30.2</v>
       </c>
       <c r="G7" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="8">
@@ -2625,16 +2625,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2650,13 +2650,13 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5986,10 +5986,10 @@
         <v>82.2</v>
       </c>
       <c r="G2" t="n">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="H2" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="3">
@@ -6017,7 +6017,7 @@
         <v>26</v>
       </c>
       <c r="H3" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="4">
@@ -6067,10 +6067,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>63.3</v>
+        <v>63.8</v>
       </c>
       <c r="G5" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="H5" t="n">
         <v>6.6</v>
@@ -6285,19 +6285,19 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>52.3</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6313,16 +6313,16 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>47.7</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -493,13 +493,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="H2" t="n">
-        <v>35.9</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="3">
@@ -521,13 +521,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>81.3</v>
       </c>
       <c r="G3" t="n">
-        <v>62.7</v>
+        <v>63.5</v>
       </c>
       <c r="H3" t="n">
-        <v>34.7</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="4">
@@ -549,13 +549,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="G4" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -577,13 +577,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>70.5</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="6">
@@ -602,16 +602,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>68.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>21.8</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -630,16 +630,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>71.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>40.1</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -658,16 +658,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>51.4</v>
+        <v>52.5</v>
       </c>
       <c r="F8" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -686,16 +686,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>77.2</v>
       </c>
       <c r="F9" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="G9" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -714,13 +714,13 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>22.8</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
@@ -742,10 +742,10 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>48.5</v>
+        <v>47.5</v>
       </c>
       <c r="F11" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>4.3</v>
@@ -767,19 +767,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="E12" t="n">
-        <v>26.2</v>
+        <v>28.2</v>
       </c>
       <c r="F12" t="n">
-        <v>11.1</v>
+        <v>12.4</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -795,16 +795,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>30.6</v>
+        <v>29.1</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -823,19 +823,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>69.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="F14" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -851,16 +851,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>84.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="E2" t="n">
-        <v>62.3</v>
+        <v>63.1</v>
       </c>
       <c r="F2" t="n">
-        <v>27.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="3">
@@ -947,13 +947,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>89.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="E3" t="n">
-        <v>71.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>52.8</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -969,13 +969,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>57.7</v>
+        <v>58.3</v>
       </c>
       <c r="E4" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="F4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="5">
@@ -991,13 +991,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>71.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E5" t="n">
-        <v>25.4</v>
+        <v>23.9</v>
       </c>
       <c r="F5" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
@@ -1013,7 +1013,7 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>28.1</v>
+        <v>31.2</v>
       </c>
       <c r="E6" t="n">
         <v>6.5</v>
@@ -1035,13 +1035,13 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>42.3</v>
+        <v>41.7</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -1057,13 +1057,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>10.6</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -1079,13 +1079,13 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>15.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -1180,13 +1180,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>64.2</v>
+        <v>66.3</v>
       </c>
       <c r="F3" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -1205,13 +1205,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>46</v>
+        <v>42.4</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="G4" t="n">
-        <v>16.3</v>
+        <v>15.7</v>
       </c>
     </row>
     <row r="5">
@@ -1258,10 +1258,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>69.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>32.4</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="7">
@@ -1280,13 +1280,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>57.6</v>
       </c>
       <c r="F7" t="n">
-        <v>33.1</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>21.3</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="8">
@@ -1305,13 +1305,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>35.8</v>
+        <v>33.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="G8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="9">
@@ -1358,10 +1358,10 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>30.6</v>
+        <v>31.4</v>
       </c>
       <c r="G10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
@@ -1481,13 +1481,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>60.4</v>
+        <v>61.3</v>
       </c>
       <c r="G2" t="n">
-        <v>38.7</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="3">
@@ -1506,13 +1506,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>39.6</v>
+        <v>38.7</v>
       </c>
       <c r="G3" t="n">
-        <v>20.1</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="4">
@@ -1531,13 +1531,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>57.4</v>
+        <v>60.8</v>
       </c>
       <c r="F4" t="n">
-        <v>27.9</v>
+        <v>31.6</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="5">
@@ -1556,13 +1556,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>57.8</v>
+        <v>58.5</v>
       </c>
       <c r="F5" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6">
@@ -1578,16 +1578,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>42.1</v>
+        <v>41.4</v>
       </c>
       <c r="F6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="7">
@@ -1603,16 +1603,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>89.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>41.5</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>19.2</v>
+        <v>17.4</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
@@ -1628,16 +1628,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>74.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="F8" t="n">
-        <v>12.3</v>
+        <v>11.4</v>
       </c>
       <c r="G8" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9">
@@ -1653,16 +1653,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>43.4</v>
+        <v>45.4</v>
       </c>
       <c r="E9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1678,16 +1678,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>56.6</v>
+        <v>54.6</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="F10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -1703,10 +1703,10 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>23.8</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
@@ -1728,10 +1728,10 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="n">
         <v>0.1</v>
@@ -1753,10 +1753,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1819,10 +1819,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>81.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>63.1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -1838,10 +1838,10 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>31.2</v>
+        <v>33.7</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4">
@@ -1857,10 +1857,10 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>68.8</v>
+        <v>66.3</v>
       </c>
       <c r="E4" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="5">
@@ -1876,10 +1876,10 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -1957,13 +1957,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>78.5</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>56.7</v>
+        <v>58.1</v>
       </c>
       <c r="H2" t="n">
-        <v>35.7</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -1985,13 +1985,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G3" t="n">
-        <v>36.2</v>
+        <v>40.9</v>
       </c>
       <c r="H3" t="n">
-        <v>18.9</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="4">
@@ -2013,13 +2013,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>51.6</v>
+        <v>55.1</v>
       </c>
       <c r="G4" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="H4" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="5">
@@ -2041,13 +2041,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>76.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="G5" t="n">
-        <v>29</v>
+        <v>27.3</v>
       </c>
       <c r="H5" t="n">
-        <v>15.6</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="6">
@@ -2066,16 +2066,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>56.3</v>
+        <v>58.3</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -2094,16 +2094,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>65.7</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>34.3</v>
+        <v>30.8</v>
       </c>
       <c r="G7" t="n">
-        <v>18.4</v>
+        <v>15.6</v>
       </c>
       <c r="H7" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="8">
@@ -2122,16 +2122,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>55.5</v>
+        <v>52.6</v>
       </c>
       <c r="F8" t="n">
-        <v>19.9</v>
+        <v>17</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -2150,16 +2150,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="F9" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="G9" t="n">
         <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -2175,19 +2175,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>81.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>43.1</v>
+        <v>42.7</v>
       </c>
       <c r="F10" t="n">
-        <v>8.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -2203,16 +2203,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>33.4</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
         <v>1.2</v>
@@ -2231,19 +2231,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>71.2</v>
+        <v>72.3</v>
       </c>
       <c r="E12" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
@@ -2259,10 +2259,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>64.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>31</v>
+        <v>34.2</v>
       </c>
       <c r="F13" t="n">
         <v>7.8</v>
@@ -2287,13 +2287,13 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>35.5</v>
+        <v>27.4</v>
       </c>
       <c r="E14" t="n">
-        <v>12.7</v>
+        <v>7.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>0.1</v>
@@ -2315,13 +2315,13 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>28.8</v>
+        <v>27.7</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G15" t="n">
         <v>0.3</v>
@@ -2343,16 +2343,16 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35.7</v>
+        <v>26.9</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
@@ -2371,10 +2371,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="F17" t="n">
         <v>0.1</v>
@@ -2453,13 +2453,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>93.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="F2" t="n">
-        <v>65.2</v>
+        <v>62.2</v>
       </c>
       <c r="G2" t="n">
-        <v>41.2</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="3">
@@ -2478,13 +2478,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>83.09999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="G3" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="4">
@@ -2503,13 +2503,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>36.2</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>13.9</v>
+        <v>18.1</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5">
@@ -2528,13 +2528,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="F5" t="n">
-        <v>18.3</v>
+        <v>20.5</v>
       </c>
       <c r="G5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="6">
@@ -2553,13 +2553,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="F6" t="n">
-        <v>15.9</v>
+        <v>16.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="7">
@@ -2578,13 +2578,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>63.8</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>30.2</v>
+        <v>25.1</v>
       </c>
       <c r="G7" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="8">
@@ -2600,16 +2600,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>70.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -2653,10 +2653,10 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2675,13 +2675,13 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -2757,10 +2757,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>81.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -2782,10 +2782,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>82.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>59.2</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="4">
@@ -2804,13 +2804,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>76.59999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>15.3</v>
+        <v>17.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5">
@@ -2832,10 +2832,10 @@
         <v>58.6</v>
       </c>
       <c r="F5" t="n">
-        <v>11.9</v>
+        <v>13.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2851,16 +2851,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>70.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>33.4</v>
+        <v>32.8</v>
       </c>
       <c r="F6" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -2876,16 +2876,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="E7" t="n">
-        <v>17.9</v>
+        <v>19.8</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -2901,10 +2901,10 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="E8" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="F8" t="n">
         <v>0.2</v>
@@ -2926,16 +2926,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>29.8</v>
+        <v>28.6</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3024,10 +3024,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="I2" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3055,10 +3055,10 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="I3" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -3083,13 +3083,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>83.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="I4" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -3114,13 +3114,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>39.7</v>
+        <v>37.4</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -3142,13 +3142,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69.3</v>
       </c>
       <c r="G6" t="n">
-        <v>43.2</v>
+        <v>46.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0.3</v>
@@ -3173,16 +3173,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>48.7</v>
+        <v>50.3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.3</v>
+        <v>5.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3201,19 +3201,19 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>82.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>46.3</v>
+        <v>43.6</v>
       </c>
       <c r="G8" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -3232,16 +3232,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>72.7</v>
+        <v>72</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>24.1</v>
       </c>
       <c r="G9" t="n">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="I9" t="n">
         <v>0.1</v>
@@ -3263,13 +3263,13 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>27.3</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
@@ -3325,13 +3325,13 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>17.9</v>
+        <v>23.5</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -3446,13 +3446,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>93.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>79.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>65.3</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="3">
@@ -3474,13 +3474,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>67.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>38.3</v>
+        <v>39.1</v>
       </c>
       <c r="H3" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -3502,13 +3502,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>37.9</v>
+        <v>39.7</v>
       </c>
       <c r="G4" t="n">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -3530,13 +3530,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>10.6</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="6">
@@ -3555,16 +3555,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>65.40000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>26.9</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -3583,16 +3583,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>71.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>49.4</v>
+        <v>47.5</v>
       </c>
       <c r="G7" t="n">
-        <v>28.3</v>
+        <v>27.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8">
@@ -3611,16 +3611,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>65.8</v>
+        <v>62.4</v>
       </c>
       <c r="F8" t="n">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -3639,13 +3639,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>52.7</v>
+        <v>57.4</v>
       </c>
       <c r="F9" t="n">
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H9" t="n">
         <v>0.2</v>
@@ -3667,10 +3667,10 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>47.3</v>
+        <v>42.6</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
         <v>0.7</v>
@@ -3692,19 +3692,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>63.7</v>
       </c>
       <c r="E11" t="n">
-        <v>23.2</v>
+        <v>27.2</v>
       </c>
       <c r="F11" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="G11" t="n">
         <v>1.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -3720,19 +3720,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>71.40000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="F12" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="G12" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -3748,19 +3748,19 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>55.7</v>
+        <v>55.5</v>
       </c>
       <c r="E13" t="n">
-        <v>19.8</v>
+        <v>18.3</v>
       </c>
       <c r="F13" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -3776,13 +3776,13 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="E14" t="n">
         <v>14.8</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0.5</v>
@@ -3804,16 +3804,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -3832,19 +3832,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36.3</v>
       </c>
       <c r="E16" t="n">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="F16" t="n">
         <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3925,10 +3925,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.3</v>
+        <v>75.3</v>
       </c>
       <c r="H2" t="n">
-        <v>49.3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -3953,10 +3953,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>32.3</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="4">
@@ -3978,13 +3978,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>72.2</v>
+        <v>71.2</v>
       </c>
       <c r="G4" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="H4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5">
@@ -4006,13 +4006,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>53.2</v>
+        <v>54.2</v>
       </c>
       <c r="G5" t="n">
-        <v>9.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="6">
@@ -4031,16 +4031,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>37.1</v>
+        <v>35.2</v>
       </c>
       <c r="G6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -4062,13 +4062,13 @@
         <v>32</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="G7" t="n">
         <v>1.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -4084,13 +4084,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>47.9</v>
+        <v>44.5</v>
       </c>
       <c r="E8" t="n">
-        <v>30.5</v>
+        <v>29.7</v>
       </c>
       <c r="F8" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -4112,19 +4112,19 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>43.7</v>
+        <v>33.7</v>
       </c>
       <c r="E9" t="n">
-        <v>12.6</v>
+        <v>8.6</v>
       </c>
       <c r="F9" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
         <v>0.2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4140,19 +4140,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>56.3</v>
+        <v>66.3</v>
       </c>
       <c r="E10" t="n">
-        <v>16.4</v>
+        <v>22.8</v>
       </c>
       <c r="F10" t="n">
-        <v>6.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -4168,19 +4168,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>52.1</v>
+        <v>55.5</v>
       </c>
       <c r="E11" t="n">
-        <v>37.5</v>
+        <v>38.3</v>
       </c>
       <c r="F11" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -4258,13 +4258,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>84.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>60.8</v>
+        <v>61.2</v>
       </c>
       <c r="H2" t="n">
-        <v>39.9</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="3">
@@ -4286,13 +4286,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>76.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>47.8</v>
+        <v>48.6</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="4">
@@ -4314,13 +4314,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>74.90000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="G4" t="n">
-        <v>36.4</v>
+        <v>36.8</v>
       </c>
       <c r="H4" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="5">
@@ -4342,13 +4342,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>68.7</v>
+        <v>70.5</v>
       </c>
       <c r="G5" t="n">
-        <v>26.2</v>
+        <v>27.9</v>
       </c>
       <c r="H5" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="6">
@@ -4370,13 +4370,13 @@
         <v>72.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -4395,16 +4395,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>52.8</v>
+        <v>55.8</v>
       </c>
       <c r="F7" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -4423,16 +4423,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>39.2</v>
+        <v>40.9</v>
       </c>
       <c r="F8" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -4454,13 +4454,13 @@
         <v>64.8</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="G9" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -4479,13 +4479,13 @@
         <v>63.7</v>
       </c>
       <c r="E10" t="n">
-        <v>28.2</v>
+        <v>26.8</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
         <v>0.2</v>
@@ -4507,16 +4507,16 @@
         <v>80.7</v>
       </c>
       <c r="E11" t="n">
-        <v>55.4</v>
+        <v>53.7</v>
       </c>
       <c r="F11" t="n">
-        <v>14.9</v>
+        <v>14.3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="12">
@@ -4532,16 +4532,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>31.8</v>
+        <v>34.3</v>
       </c>
       <c r="E12" t="n">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="F12" t="n">
         <v>1.7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -4560,13 +4560,13 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>52.3</v>
+        <v>53.2</v>
       </c>
       <c r="E13" t="n">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
         <v>0.4</v>
@@ -4588,13 +4588,13 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>47.7</v>
+        <v>46.8</v>
       </c>
       <c r="E14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
         <v>0.4</v>
@@ -4616,19 +4616,19 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>68.2</v>
+        <v>65.7</v>
       </c>
       <c r="E15" t="n">
-        <v>35.9</v>
+        <v>33.8</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -4644,13 +4644,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G16" t="n">
         <v>0.1</v>
@@ -4675,10 +4675,10 @@
         <v>36.3</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
         <v>0.1</v>
@@ -4754,13 +4754,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>87.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>69.5</v>
+        <v>68.5</v>
       </c>
       <c r="G2" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3">
@@ -4779,13 +4779,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>85.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>61.3</v>
       </c>
       <c r="G3" t="n">
-        <v>35.8</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="4">
@@ -4804,13 +4804,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>74.3</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>27.2</v>
+        <v>28.5</v>
       </c>
       <c r="G4" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="5">
@@ -4829,13 +4829,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>56</v>
+        <v>57.1</v>
       </c>
       <c r="F5" t="n">
-        <v>15.5</v>
+        <v>16.2</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
@@ -4854,13 +4854,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>42.9</v>
       </c>
       <c r="F6" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -4876,16 +4876,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>43.5</v>
+        <v>45.1</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="F7" t="n">
         <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -4901,13 +4901,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>56.3</v>
+        <v>57.5</v>
       </c>
       <c r="E8" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
         <v>0.8</v>
@@ -4926,13 +4926,13 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>56.4</v>
+        <v>56.2</v>
       </c>
       <c r="E9" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
         <v>0.8</v>
@@ -4951,13 +4951,13 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
@@ -4976,16 +4976,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>43.7</v>
+        <v>42.5</v>
       </c>
       <c r="E11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="F11" t="n">
         <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -5001,13 +5001,13 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>56.5</v>
+        <v>54.9</v>
       </c>
       <c r="E12" t="n">
-        <v>14.7</v>
+        <v>14.2</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
         <v>0.6</v>
@@ -5083,10 +5083,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>89.8</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>76.7</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="3">
@@ -5105,13 +5105,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>73.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>57.4</v>
+        <v>64.2</v>
       </c>
       <c r="G3" t="n">
-        <v>14.9</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="4">
@@ -5130,13 +5130,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>59.3</v>
+        <v>59.6</v>
       </c>
       <c r="F4" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -5155,13 +5155,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>51.5</v>
+        <v>47.8</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -5180,13 +5180,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>48.5</v>
+        <v>52.2</v>
       </c>
       <c r="F6" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -5205,13 +5205,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -5230,13 +5230,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>26.2</v>
+        <v>18.6</v>
       </c>
       <c r="F8" t="n">
-        <v>13.3</v>
+        <v>9.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -5372,13 +5372,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>77.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>45.8</v>
+        <v>46.2</v>
       </c>
       <c r="I2" t="n">
-        <v>31.9</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="3">
@@ -5403,13 +5403,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>73.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I3" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="4">
@@ -5434,13 +5434,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>61</v>
+        <v>60.7</v>
       </c>
       <c r="H4" t="n">
-        <v>26.5</v>
+        <v>24.9</v>
       </c>
       <c r="I4" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5">
@@ -5465,13 +5465,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="H5" t="n">
-        <v>29.4</v>
+        <v>29.9</v>
       </c>
       <c r="I5" t="n">
-        <v>18.1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -5493,16 +5493,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>84.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="G6" t="n">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="H6" t="n">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="I6" t="n">
-        <v>11.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7">
@@ -5524,16 +5524,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>69.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>32.2</v>
       </c>
       <c r="H7" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -5555,16 +5555,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>60.2</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="H8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9">
@@ -5586,16 +5586,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="G9" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
@@ -5617,16 +5617,16 @@
         <v>79.8</v>
       </c>
       <c r="F10" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>11.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -5645,16 +5645,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>64.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>28.3</v>
+        <v>32.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I11" t="n">
         <v>0.5</v>
@@ -5676,19 +5676,19 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>70.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>26.5</v>
+        <v>23.5</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -5707,10 +5707,10 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>56.5</v>
+        <v>54.3</v>
       </c>
       <c r="F13" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
@@ -5738,19 +5738,19 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>43.5</v>
+        <v>45.7</v>
       </c>
       <c r="F14" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15">
@@ -5769,13 +5769,13 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>29.6</v>
+        <v>27.4</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
@@ -5797,19 +5797,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>71.90000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="E16" t="n">
-        <v>29.7</v>
+        <v>22.6</v>
       </c>
       <c r="F16" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="n">
         <v>0.1</v>
@@ -5828,19 +5828,19 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>59.8</v>
+        <v>60.1</v>
       </c>
       <c r="E17" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="F17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5859,13 +5859,13 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>40.2</v>
+        <v>39.9</v>
       </c>
       <c r="E18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -5890,16 +5890,16 @@
         <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>28.1</v>
+        <v>31.8</v>
       </c>
       <c r="E19" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -5983,13 +5983,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>82.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>64.3</v>
+        <v>64.8</v>
       </c>
       <c r="H2" t="n">
-        <v>36.8</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="3">
@@ -6011,13 +6011,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="H3" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="4">
@@ -6039,13 +6039,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>69.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>46.4</v>
       </c>
       <c r="H4" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="5">
@@ -6067,13 +6067,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>63.8</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="H5" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6">
@@ -6092,16 +6092,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>71.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
@@ -6123,13 +6123,13 @@
         <v>63.6</v>
       </c>
       <c r="F7" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -6148,16 +6148,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>74.3</v>
+        <v>76.3</v>
       </c>
       <c r="F8" t="n">
         <v>35.2</v>
       </c>
       <c r="G8" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="9">
@@ -6176,16 +6176,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>39.8</v>
+        <v>44.8</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -6204,16 +6204,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>60.2</v>
+        <v>55.2</v>
       </c>
       <c r="F10" t="n">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -6232,16 +6232,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>25.7</v>
+        <v>23.7</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -6263,13 +6263,13 @@
         <v>36.4</v>
       </c>
       <c r="F12" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -6316,13 +6316,13 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>28.5</v>
+        <v>33.6</v>
       </c>
       <c r="F14" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
@@ -6395,13 +6395,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>79.5</v>
       </c>
       <c r="F2" t="n">
-        <v>49.6</v>
+        <v>53.1</v>
       </c>
       <c r="G2" t="n">
-        <v>28.7</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="3">
@@ -6420,13 +6420,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="F3" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="G3" t="n">
-        <v>24.5</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4">
@@ -6445,13 +6445,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>72.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>36.4</v>
+        <v>35.4</v>
       </c>
       <c r="G4" t="n">
-        <v>19.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="5">
@@ -6470,13 +6470,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>48.5</v>
+        <v>47.4</v>
       </c>
       <c r="F5" t="n">
-        <v>19.9</v>
+        <v>18.7</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6">
@@ -6495,13 +6495,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="F6" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="G6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="7">
@@ -6520,13 +6520,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>27.7</v>
+        <v>28.4</v>
       </c>
       <c r="F7" t="n">
-        <v>7.3</v>
+        <v>8.4</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -6542,13 +6542,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>43.4</v>
+        <v>42.2</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G8" t="n">
         <v>1.1</v>
@@ -6567,16 +6567,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47.2</v>
       </c>
       <c r="E9" t="n">
-        <v>13.4</v>
+        <v>10.7</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -6592,16 +6592,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
       <c r="E10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -6617,16 +6617,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>56.6</v>
+        <v>57.8</v>
       </c>
       <c r="E11" t="n">
-        <v>20.4</v>
+        <v>16.8</v>
       </c>
       <c r="F11" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -496,10 +496,10 @@
         <v>76.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>55.9</v>
+        <v>56.7</v>
       </c>
       <c r="H2" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="3">
@@ -577,13 +577,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>63.2</v>
       </c>
       <c r="G5" t="n">
-        <v>24.7</v>
+        <v>22.1</v>
       </c>
       <c r="H5" t="n">
-        <v>11.7</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="6">
@@ -605,13 +605,13 @@
         <v>70.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>29.8</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -636,7 +636,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.5</v>
@@ -667,7 +667,7 @@
         <v>4.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -692,10 +692,10 @@
         <v>21.8</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="10">
@@ -928,10 +928,10 @@
         <v>83.3</v>
       </c>
       <c r="E2" t="n">
-        <v>63.1</v>
+        <v>60.7</v>
       </c>
       <c r="F2" t="n">
-        <v>32.7</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="3">
@@ -947,13 +947,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>70.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="4">
@@ -969,13 +969,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>58.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>14.9</v>
+        <v>17.4</v>
       </c>
       <c r="F4" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5">
@@ -991,13 +991,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>68.8</v>
+        <v>56.6</v>
       </c>
       <c r="E5" t="n">
-        <v>23.9</v>
+        <v>20.2</v>
       </c>
       <c r="F5" t="n">
-        <v>7.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -1006,20 +1006,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ohio</t>
+          <t>Bowling Green</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>31.2</v>
+        <v>43.4</v>
       </c>
       <c r="E6" t="n">
-        <v>6.5</v>
+        <v>13.6</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -1028,20 +1028,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bowling Green</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>41.7</v>
+        <v>26.6</v>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>4.2</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1057,13 +1057,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
@@ -1082,10 +1082,10 @@
         <v>16.7</v>
       </c>
       <c r="E9" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -1183,10 +1183,10 @@
         <v>66.3</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="G3" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="4">
@@ -1211,7 +1211,7 @@
         <v>25.5</v>
       </c>
       <c r="G4" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="5">
@@ -1258,10 +1258,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>68.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="G6" t="n">
-        <v>30.1</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="7">
@@ -1283,10 +1283,10 @@
         <v>57.6</v>
       </c>
       <c r="F7" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="G7" t="n">
-        <v>24.3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="8">
@@ -1308,7 +1308,7 @@
         <v>33.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="G8" t="n">
         <v>4.6</v>
@@ -1358,10 +1358,10 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>31.4</v>
+        <v>33.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11">
@@ -1484,10 +1484,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>61.3</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>40.4</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="3">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>San Diego St</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1506,13 +1506,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="F3" t="n">
-        <v>38.7</v>
+        <v>39.1</v>
       </c>
       <c r="G3" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Diego St</t>
+          <t>New Mexico</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1531,13 +1531,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>60.8</v>
+        <v>67.5</v>
       </c>
       <c r="F4" t="n">
-        <v>31.6</v>
+        <v>39.8</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -1556,13 +1556,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>58.5</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>15.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colorado St</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1581,13 +1581,13 @@
         <v>96.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>41.4</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>12.5</v>
+        <v>19.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1606,13 +1606,13 @@
         <v>88.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>31.2</v>
       </c>
       <c r="F7" t="n">
-        <v>17.4</v>
+        <v>12.3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Colorado St</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>76.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E8" t="n">
-        <v>27.6</v>
+        <v>22.7</v>
       </c>
       <c r="F8" t="n">
-        <v>11.4</v>
+        <v>7.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -1659,10 +1659,10 @@
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -1684,10 +1684,10 @@
         <v>10.4</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1703,10 +1703,10 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>23.8</v>
+        <v>27.3</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="F11" t="n">
         <v>0.9</v>
@@ -2459,7 +2459,7 @@
         <v>62.2</v>
       </c>
       <c r="G2" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="3">
@@ -2481,10 +2481,10 @@
         <v>79.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="G3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="4">
@@ -2531,10 +2531,10 @@
         <v>55.1</v>
       </c>
       <c r="F5" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="G5" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="6">
@@ -2556,7 +2556,7 @@
         <v>44.9</v>
       </c>
       <c r="F6" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="G6" t="n">
         <v>6.6</v>
@@ -2581,7 +2581,7 @@
         <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="G7" t="n">
         <v>10.4</v>
@@ -2600,13 +2600,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>71.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="F8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G8" t="n">
         <v>0.9</v>
@@ -2656,7 +2656,7 @@
         <v>7.4</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2675,13 +2675,13 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>28.1</v>
+        <v>27.4</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="I2" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="3">
@@ -3114,7 +3114,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
@@ -3142,10 +3142,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="G6" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -3173,10 +3173,10 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="n">
         <v>0.4</v>
@@ -3232,13 +3232,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>72</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.7</v>
@@ -3263,13 +3263,13 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>30.4</v>
       </c>
       <c r="F10" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
@@ -3328,7 +3328,7 @@
         <v>23.5</v>
       </c>
       <c r="F12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G12" t="n">
         <v>0.3</v>
@@ -4258,13 +4258,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>85.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="G2" t="n">
-        <v>61.2</v>
+        <v>62.7</v>
       </c>
       <c r="H2" t="n">
-        <v>41.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -4286,13 +4286,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>77.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="H3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="4">
@@ -4317,10 +4317,10 @@
         <v>75.5</v>
       </c>
       <c r="G4" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="H4" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="5">
@@ -4345,10 +4345,10 @@
         <v>70.5</v>
       </c>
       <c r="G5" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="H5" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="6">
@@ -4373,10 +4373,10 @@
         <v>24.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -4401,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>0.5</v>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4423,16 +4423,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>40.9</v>
+        <v>41.4</v>
       </c>
       <c r="F8" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4451,16 +4451,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>64.8</v>
+        <v>49.9</v>
       </c>
       <c r="F9" t="n">
-        <v>11.4</v>
+        <v>7.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10">
@@ -4469,26 +4469,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>63.7</v>
+        <v>74.2</v>
       </c>
       <c r="E10" t="n">
-        <v>26.8</v>
+        <v>41.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -4507,16 +4507,16 @@
         <v>80.7</v>
       </c>
       <c r="E11" t="n">
-        <v>53.7</v>
+        <v>53.5</v>
       </c>
       <c r="F11" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="G11" t="n">
         <v>6.9</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -4647,7 +4647,7 @@
         <v>19.3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="F16" t="n">
         <v>0.6</v>
@@ -4672,13 +4672,13 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="E17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G17" t="n">
         <v>0.1</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>St John's</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4754,13 +4754,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>85.90000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="F2" t="n">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="G2" t="n">
-        <v>43</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="3">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>St John's</t>
+          <t>Connecticut</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4779,13 +4779,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>61.3</v>
+        <v>66.7</v>
       </c>
       <c r="G3" t="n">
-        <v>34.7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -4807,10 +4807,10 @@
         <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>28.5</v>
+        <v>24.2</v>
       </c>
       <c r="G4" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="5">
@@ -4832,10 +4832,10 @@
         <v>57.1</v>
       </c>
       <c r="F5" t="n">
-        <v>16.2</v>
+        <v>17.1</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4857,7 +4857,7 @@
         <v>42.9</v>
       </c>
       <c r="F6" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="G6" t="n">
         <v>2.6</v>
@@ -4882,10 +4882,10 @@
         <v>10.8</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -4904,10 +4904,10 @@
         <v>57.5</v>
       </c>
       <c r="E8" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0.8</v>
@@ -4932,7 +4932,7 @@
         <v>9.1</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="n">
         <v>0.8</v>
@@ -4954,10 +4954,10 @@
         <v>43.8</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
         <v>0.4</v>
@@ -4979,10 +4979,10 @@
         <v>42.5</v>
       </c>
       <c r="E11" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="G11" t="n">
         <v>0.4</v>
@@ -5007,10 +5007,10 @@
         <v>14.2</v>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -5083,10 +5083,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>73.8</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="3">
@@ -5105,13 +5105,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="F3" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="4">
@@ -5158,10 +5158,10 @@
         <v>47.8</v>
       </c>
       <c r="F5" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -5186,7 +5186,7 @@
         <v>5.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="7">
@@ -5211,7 +5211,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -5230,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F8" t="n">
         <v>9.4</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -493,13 +493,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>76.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>56.7</v>
+        <v>54.6</v>
       </c>
       <c r="H2" t="n">
-        <v>36.7</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="3">
@@ -524,10 +524,10 @@
         <v>81.3</v>
       </c>
       <c r="G3" t="n">
-        <v>63.5</v>
+        <v>63.1</v>
       </c>
       <c r="H3" t="n">
-        <v>35.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4">
@@ -549,10 +549,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="H4" t="n">
         <v>2.9</v>
@@ -577,13 +577,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>63.2</v>
+        <v>60.9</v>
       </c>
       <c r="G5" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="H5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -602,16 +602,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="F6" t="n">
-        <v>29.8</v>
+        <v>32.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="7">
@@ -636,10 +636,10 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="8">
@@ -658,7 +658,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -676,7 +676,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G Washington</t>
+          <t>Fordham</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -686,16 +686,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>77.2</v>
+        <v>24.9</v>
       </c>
       <c r="F9" t="n">
-        <v>21.8</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>10.7</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -704,7 +704,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>G Washington</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -714,16 +714,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>22.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>20.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>10.3</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="11">
@@ -742,13 +742,13 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="F11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0.8</v>
@@ -767,19 +767,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>28.2</v>
       </c>
       <c r="F12" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="13">
@@ -795,16 +795,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>29.1</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="F13" t="n">
         <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -823,19 +823,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>70.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="E14" t="n">
-        <v>24.2</v>
+        <v>22.1</v>
       </c>
       <c r="F14" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -851,7 +851,7 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="E15" t="n">
         <v>1.9</v>
@@ -1186,7 +1186,7 @@
         <v>27.3</v>
       </c>
       <c r="G3" t="n">
-        <v>16.4</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="4">
@@ -1211,7 +1211,7 @@
         <v>25.5</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="5">
@@ -1258,10 +1258,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>66.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>28.9</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="7">
@@ -1283,10 +1283,10 @@
         <v>57.6</v>
       </c>
       <c r="F7" t="n">
-        <v>36.8</v>
+        <v>37.1</v>
       </c>
       <c r="G7" t="n">
-        <v>24.8</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="8">
@@ -1308,10 +1308,10 @@
         <v>33.7</v>
       </c>
       <c r="F8" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="9">
@@ -1358,10 +1358,10 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>33.7</v>
+        <v>31.4</v>
       </c>
       <c r="G10" t="n">
-        <v>9.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="11">
@@ -1484,10 +1484,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>59.6</v>
       </c>
       <c r="G2" t="n">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="3">
@@ -1506,13 +1506,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>72.8</v>
+        <v>74.5</v>
       </c>
       <c r="F3" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="G3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="4">
@@ -1534,10 +1534,10 @@
         <v>67.5</v>
       </c>
       <c r="F4" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="5">
@@ -1556,13 +1556,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>46.9</v>
+        <v>45.7</v>
       </c>
       <c r="F5" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -1578,16 +1578,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>96.59999999999999</v>
+        <v>99</v>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>54.3</v>
       </c>
       <c r="F6" t="n">
-        <v>19.2</v>
+        <v>20.3</v>
       </c>
       <c r="G6" t="n">
-        <v>9.300000000000001</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="7">
@@ -1609,10 +1609,10 @@
         <v>31.2</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="8">
@@ -1631,13 +1631,13 @@
         <v>72.7</v>
       </c>
       <c r="E8" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -1659,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
         <v>0.9</v>
@@ -1684,10 +1684,10 @@
         <v>10.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11">
@@ -1712,7 +1712,7 @@
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12">
@@ -1753,10 +1753,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1957,13 +1957,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>82.2</v>
       </c>
       <c r="G2" t="n">
-        <v>58.1</v>
+        <v>59.5</v>
       </c>
       <c r="H2" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="3">
@@ -1985,13 +1985,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>70.5</v>
+        <v>69.2</v>
       </c>
       <c r="G3" t="n">
-        <v>40.9</v>
+        <v>43.8</v>
       </c>
       <c r="H3" t="n">
-        <v>20.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2013,13 +2013,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>55.1</v>
+        <v>68.8</v>
       </c>
       <c r="G4" t="n">
-        <v>27.6</v>
+        <v>32.9</v>
       </c>
       <c r="H4" t="n">
-        <v>11.3</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="5">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Vanderbilt</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2041,13 +2041,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>77.7</v>
+        <v>52.5</v>
       </c>
       <c r="G5" t="n">
-        <v>27.3</v>
+        <v>17.5</v>
       </c>
       <c r="H5" t="n">
-        <v>14.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2066,16 +2066,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>58.3</v>
+        <v>63.9</v>
       </c>
       <c r="F6" t="n">
-        <v>13.5</v>
+        <v>33.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>11.6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vanderbilt</t>
+          <t>Texas A&amp;M</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2094,16 +2094,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>66.40000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="F7" t="n">
-        <v>30.8</v>
+        <v>21.3</v>
       </c>
       <c r="G7" t="n">
-        <v>15.6</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Texas A&amp;M</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2122,16 +2122,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>52.6</v>
+        <v>60.1</v>
       </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Missouri</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2150,16 +2150,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>53.9</v>
+        <v>39.3</v>
       </c>
       <c r="F9" t="n">
-        <v>12.7</v>
+        <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -2168,26 +2168,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>82.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>42.7</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>10.2</v>
+        <v>11.8</v>
       </c>
       <c r="G10" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -2206,16 +2206,16 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>32.3</v>
       </c>
       <c r="F11" t="n">
-        <v>10.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -2224,26 +2224,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Auburn</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>72.3</v>
+        <v>76.8</v>
       </c>
       <c r="E12" t="n">
-        <v>29.1</v>
+        <v>32.9</v>
       </c>
       <c r="F12" t="n">
-        <v>13.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -2252,26 +2252,26 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Auburn</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>72.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="E13" t="n">
-        <v>34.2</v>
+        <v>33.3</v>
       </c>
       <c r="F13" t="n">
-        <v>7.8</v>
+        <v>13.3</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="14">
@@ -2287,16 +2287,16 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>27.4</v>
+        <v>19.5</v>
       </c>
       <c r="E14" t="n">
-        <v>7.6</v>
+        <v>2.9</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -2308,26 +2308,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mississippi</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>27.7</v>
+        <v>23.2</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>Mississippi</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2346,10 +2346,10 @@
         <v>26.9</v>
       </c>
       <c r="E16" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
         <v>0.4</v>
@@ -2364,26 +2364,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>17.6</v>
+        <v>25.9</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4</v>
+        <v>10.8</v>
       </c>
       <c r="F17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2459,7 +2459,7 @@
         <v>62.2</v>
       </c>
       <c r="G2" t="n">
-        <v>39.3</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="3">
@@ -2478,13 +2478,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>79.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>51.6</v>
+        <v>49.3</v>
       </c>
       <c r="G3" t="n">
-        <v>26.2</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="4">
@@ -2503,13 +2503,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>42.1</v>
       </c>
       <c r="F4" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5">
@@ -2534,7 +2534,7 @@
         <v>20.2</v>
       </c>
       <c r="G5" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="6">
@@ -2578,13 +2578,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>57.9</v>
       </c>
       <c r="F7" t="n">
-        <v>24.8</v>
+        <v>27.9</v>
       </c>
       <c r="G7" t="n">
-        <v>10.4</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="8">
@@ -2600,16 +2600,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>72.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="E8" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2675,16 +2675,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>27.4</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F11" t="n">
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3024,10 +3024,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>96.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>65.5</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="3">
@@ -3055,10 +3055,10 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>67.5</v>
+        <v>67.8</v>
       </c>
       <c r="I3" t="n">
-        <v>25</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="4">
@@ -3083,10 +3083,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>84.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="H4" t="n">
-        <v>31.2</v>
+        <v>30.8</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -3148,7 +3148,7 @@
         <v>46.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="I6" t="n">
         <v>0.3</v>
@@ -3176,13 +3176,13 @@
         <v>50.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8">
@@ -3207,13 +3207,13 @@
         <v>43.6</v>
       </c>
       <c r="G8" t="n">
-        <v>9.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H8" t="n">
         <v>0.8</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3449,10 +3449,10 @@
         <v>93.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>83.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="H2" t="n">
-        <v>70.5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -3474,13 +3474,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="G3" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="4">
@@ -3502,13 +3502,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>39.7</v>
+        <v>38.1</v>
       </c>
       <c r="G4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -3530,13 +3530,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>66.8</v>
+        <v>62.9</v>
       </c>
       <c r="G5" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6">
@@ -3555,16 +3555,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>66.90000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>25.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -3583,16 +3583,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>71.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>47.5</v>
+        <v>51.9</v>
       </c>
       <c r="G7" t="n">
-        <v>27.7</v>
+        <v>30.6</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3611,16 +3611,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>62.4</v>
+        <v>61.3</v>
       </c>
       <c r="F8" t="n">
-        <v>22.3</v>
+        <v>21.9</v>
       </c>
       <c r="G8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
@@ -3673,7 +3673,7 @@
         <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H10" t="n">
         <v>0.2</v>
@@ -3695,16 +3695,16 @@
         <v>63.7</v>
       </c>
       <c r="E11" t="n">
-        <v>27.2</v>
+        <v>28.4</v>
       </c>
       <c r="F11" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -3720,19 +3720,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>72.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="E12" t="n">
-        <v>23.9</v>
+        <v>19.3</v>
       </c>
       <c r="F12" t="n">
-        <v>11.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -3751,16 +3751,16 @@
         <v>55.5</v>
       </c>
       <c r="E13" t="n">
-        <v>18.3</v>
+        <v>22.9</v>
       </c>
       <c r="F13" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="14">
@@ -3779,10 +3779,10 @@
         <v>44.5</v>
       </c>
       <c r="E14" t="n">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="G14" t="n">
         <v>0.5</v>
@@ -3804,13 +3804,13 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>27.6</v>
+        <v>32.3</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
         <v>0.3</v>
@@ -3841,7 +3841,7 @@
         <v>1.6</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3925,10 +3925,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>75.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>46</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="3">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3953,10 +3953,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>68.40000000000001</v>
+        <v>48.2</v>
       </c>
       <c r="H3" t="n">
-        <v>34.4</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="4">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wichita St</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3978,13 +3978,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>71.2</v>
+        <v>74.2</v>
       </c>
       <c r="G4" t="n">
-        <v>24.5</v>
+        <v>43.3</v>
       </c>
       <c r="H4" t="n">
-        <v>9.9</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="5">
@@ -4006,13 +4006,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>54.2</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FL Atlantic</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4031,16 +4031,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>68.59999999999999</v>
+        <v>46.4</v>
       </c>
       <c r="F6" t="n">
-        <v>35.2</v>
+        <v>13.1</v>
       </c>
       <c r="G6" t="n">
-        <v>9.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4059,16 +4059,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>44.7</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8</v>
+        <v>10.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -4077,26 +4077,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>FL Atlantic</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>44.5</v>
+        <v>53.1</v>
       </c>
       <c r="E8" t="n">
-        <v>29.7</v>
+        <v>29.4</v>
       </c>
       <c r="F8" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -4115,16 +4115,16 @@
         <v>33.7</v>
       </c>
       <c r="E9" t="n">
-        <v>8.6</v>
+        <v>15.8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -4143,16 +4143,16 @@
         <v>66.3</v>
       </c>
       <c r="E10" t="n">
-        <v>22.8</v>
+        <v>37.8</v>
       </c>
       <c r="F10" t="n">
-        <v>8.199999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
@@ -4168,19 +4168,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>55.5</v>
+        <v>46.9</v>
       </c>
       <c r="E11" t="n">
-        <v>38.3</v>
+        <v>25.9</v>
       </c>
       <c r="F11" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -4258,13 +4258,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>87.2</v>
+        <v>86.2</v>
       </c>
       <c r="G2" t="n">
-        <v>62.7</v>
+        <v>60.8</v>
       </c>
       <c r="H2" t="n">
-        <v>42</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="3">
@@ -4286,13 +4286,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>78</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>48.9</v>
+        <v>56.1</v>
       </c>
       <c r="H3" t="n">
-        <v>24.2</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="4">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Texas Tech</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4314,13 +4314,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>75.5</v>
+        <v>69.5</v>
       </c>
       <c r="G4" t="n">
-        <v>37</v>
+        <v>26.1</v>
       </c>
       <c r="H4" t="n">
-        <v>13.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iowa St</t>
+          <t>Texas Tech</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4342,13 +4342,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>70.5</v>
+        <v>53.3</v>
       </c>
       <c r="G5" t="n">
-        <v>27.2</v>
+        <v>18.4</v>
       </c>
       <c r="H5" t="n">
-        <v>13.9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Iowa St</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4367,16 +4367,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>72.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="F6" t="n">
-        <v>24.9</v>
+        <v>41.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>16.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7">
@@ -4395,16 +4395,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>55.8</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>22.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cincinnati</t>
+          <t>West Virginia</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4423,10 +4423,10 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>41.4</v>
+        <v>33.5</v>
       </c>
       <c r="F8" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>West Virginia</t>
+          <t>UCF</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4451,16 +4451,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>49.9</v>
+        <v>54.1</v>
       </c>
       <c r="F9" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -4469,26 +4469,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UCF</t>
+          <t>Cincinnati</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>74.2</v>
+        <v>80.3</v>
       </c>
       <c r="E10" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="11">
@@ -4504,19 +4504,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>80.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>53.5</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>14.2</v>
+        <v>16.2</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -4532,19 +4532,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>34.3</v>
+        <v>50.5</v>
       </c>
       <c r="E12" t="n">
-        <v>10.5</v>
+        <v>15.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="G12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H12" t="n">
         <v>0.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4560,19 +4560,19 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>53.2</v>
+        <v>36.2</v>
       </c>
       <c r="E13" t="n">
-        <v>14.4</v>
+        <v>6.2</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4581,26 +4581,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oklahoma St</t>
+          <t>Baylor</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>46.8</v>
+        <v>63.8</v>
       </c>
       <c r="E14" t="n">
-        <v>13.2</v>
+        <v>15.6</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -4609,26 +4609,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Oklahoma St</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>65.7</v>
+        <v>49.5</v>
       </c>
       <c r="E15" t="n">
-        <v>33.8</v>
+        <v>16.4</v>
       </c>
       <c r="F15" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -4644,16 +4644,16 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>19.3</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -4672,16 +4672,16 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>25.8</v>
+        <v>19.7</v>
       </c>
       <c r="E17" t="n">
-        <v>8.6</v>
+        <v>4.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -4754,13 +4754,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>84.7</v>
+        <v>84</v>
       </c>
       <c r="F2" t="n">
-        <v>66.5</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>34.8</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="3">
@@ -4779,13 +4779,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="F3" t="n">
-        <v>66.7</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="4">
@@ -4804,13 +4804,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>24.2</v>
+        <v>25.7</v>
       </c>
       <c r="G4" t="n">
-        <v>10.3</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
@@ -4832,10 +4832,10 @@
         <v>57.1</v>
       </c>
       <c r="F5" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -4879,10 +4879,10 @@
         <v>45.1</v>
       </c>
       <c r="E7" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
         <v>0.4</v>
@@ -4894,23 +4894,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>57.5</v>
+        <v>53.4</v>
       </c>
       <c r="E8" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9">
@@ -4926,16 +4926,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>56.2</v>
+        <v>46.5</v>
       </c>
       <c r="E9" t="n">
-        <v>9.1</v>
+        <v>7.4</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
@@ -4944,23 +4944,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>43.8</v>
+        <v>53.5</v>
       </c>
       <c r="E10" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
@@ -4969,20 +4969,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>42.5</v>
+        <v>46.6</v>
       </c>
       <c r="E11" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
         <v>0.4</v>
@@ -5004,13 +5004,13 @@
         <v>54.9</v>
       </c>
       <c r="E12" t="n">
-        <v>14.2</v>
+        <v>13.3</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -5086,7 +5086,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -5105,13 +5105,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>81.3</v>
+        <v>76.8</v>
       </c>
       <c r="F3" t="n">
-        <v>64.09999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="G3" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -5133,10 +5133,10 @@
         <v>59.6</v>
       </c>
       <c r="F4" t="n">
-        <v>17.4</v>
+        <v>18.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -5155,13 +5155,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>47.8</v>
+        <v>53.4</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -5180,10 +5180,10 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>52.2</v>
+        <v>46.6</v>
       </c>
       <c r="F6" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="G6" t="n">
         <v>1.8</v>
@@ -5208,10 +5208,10 @@
         <v>40.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5230,13 +5230,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>18.7</v>
+        <v>23.2</v>
       </c>
       <c r="F8" t="n">
-        <v>9.4</v>
+        <v>11.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -5372,13 +5372,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>78.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="H2" t="n">
-        <v>46.2</v>
+        <v>47.7</v>
       </c>
       <c r="I2" t="n">
-        <v>32.8</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="3">
@@ -5403,13 +5403,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>75.3</v>
+        <v>53.7</v>
       </c>
       <c r="H3" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>22.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="4">
@@ -5434,13 +5434,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>60.7</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
-        <v>24.9</v>
+        <v>22.7</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5">
@@ -5465,13 +5465,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>60.1</v>
+        <v>76.3</v>
       </c>
       <c r="H5" t="n">
-        <v>29.9</v>
+        <v>38.1</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="6">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5493,16 +5493,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>86.3</v>
+        <v>74.2</v>
       </c>
       <c r="G6" t="n">
-        <v>38.3</v>
+        <v>20.9</v>
       </c>
       <c r="H6" t="n">
-        <v>17.8</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5524,16 +5524,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>72.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>32.2</v>
+        <v>33.9</v>
       </c>
       <c r="H7" t="n">
-        <v>11.8</v>
+        <v>9.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Purdue</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5555,16 +5555,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>60.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>15.9</v>
+        <v>42.8</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>28.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="9">
@@ -5586,16 +5586,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="G9" t="n">
-        <v>9.699999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5614,16 +5614,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>44.4</v>
+        <v>44.2</v>
       </c>
       <c r="G10" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
@@ -5648,16 +5648,16 @@
         <v>69.90000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>32.2</v>
+        <v>16.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4</v>
+        <v>2.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5676,19 +5676,19 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>72.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="F12" t="n">
-        <v>23.5</v>
+        <v>18.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5707,19 +5707,19 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>54.3</v>
+        <v>57</v>
       </c>
       <c r="F13" t="n">
-        <v>9.4</v>
+        <v>15.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5738,16 +5738,16 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>45.7</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
         <v>0.1</v>
@@ -5769,13 +5769,13 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>27.4</v>
+        <v>33.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
@@ -5803,16 +5803,16 @@
         <v>22.6</v>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -5828,13 +5828,13 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>60.1</v>
+        <v>64.7</v>
       </c>
       <c r="E17" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="G17" t="n">
         <v>0.5</v>
@@ -5859,13 +5859,13 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>39.9</v>
+        <v>35.3</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -5896,10 +5896,10 @@
         <v>7.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -5983,13 +5983,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>81.90000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="G2" t="n">
-        <v>64.8</v>
+        <v>62.9</v>
       </c>
       <c r="H2" t="n">
-        <v>38.2</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="3">
@@ -6011,13 +6011,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="G3" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="H3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -6039,13 +6039,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>70.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="G4" t="n">
-        <v>46.4</v>
+        <v>45.7</v>
       </c>
       <c r="H4" t="n">
-        <v>28.1</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="5">
@@ -6070,10 +6070,10 @@
         <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
@@ -6098,10 +6098,10 @@
         <v>27.3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -6120,16 +6120,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>63.6</v>
+        <v>66.5</v>
       </c>
       <c r="F7" t="n">
-        <v>20.7</v>
+        <v>22.8</v>
       </c>
       <c r="G7" t="n">
-        <v>10.7</v>
+        <v>11.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="8">
@@ -6148,16 +6148,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="G8" t="n">
         <v>13.8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -6176,13 +6176,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>44.8</v>
+        <v>42.9</v>
       </c>
       <c r="F9" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H9" t="n">
         <v>0.8</v>
@@ -6204,16 +6204,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>55.2</v>
+        <v>57.1</v>
       </c>
       <c r="F10" t="n">
-        <v>10.7</v>
+        <v>13.3</v>
       </c>
       <c r="G10" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -6232,16 +6232,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -6260,16 +6260,16 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>36.4</v>
+        <v>33.5</v>
       </c>
       <c r="F12" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -6325,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -6395,13 +6395,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>53.1</v>
+        <v>54.1</v>
       </c>
       <c r="G2" t="n">
-        <v>30.5</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="3">
@@ -6420,13 +6420,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>72.3</v>
+        <v>71.7</v>
       </c>
       <c r="F3" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="G3" t="n">
-        <v>25.2</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="4">
@@ -6445,13 +6445,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>71.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
-        <v>35.4</v>
+        <v>33.1</v>
       </c>
       <c r="G4" t="n">
-        <v>18.9</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="5">
@@ -6473,10 +6473,10 @@
         <v>47.4</v>
       </c>
       <c r="F5" t="n">
-        <v>18.7</v>
+        <v>18.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6">
@@ -6498,10 +6498,10 @@
         <v>52.6</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="G6" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -6520,13 +6520,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>28.4</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
-        <v>8.4</v>
+        <v>9.9</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -6545,13 +6545,13 @@
         <v>42.2</v>
       </c>
       <c r="E8" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -6567,16 +6567,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>47.2</v>
+        <v>44.9</v>
       </c>
       <c r="E9" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -6592,16 +6592,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>52.8</v>
+        <v>55.1</v>
       </c>
       <c r="E10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -6620,13 +6620,13 @@
         <v>57.8</v>
       </c>
       <c r="E11" t="n">
-        <v>16.8</v>
+        <v>18.1</v>
       </c>
       <c r="F11" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -1819,10 +1819,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>81.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1838,10 +1838,10 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>33.7</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -1857,10 +1857,10 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>66.3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>21.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1876,10 +1876,10 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>9.1</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2453,13 +2453,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>62.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>39.4</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
@@ -2484,7 +2484,7 @@
         <v>49.3</v>
       </c>
       <c r="G3" t="n">
-        <v>25.1</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="4">
@@ -2509,7 +2509,7 @@
         <v>17.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="5">
@@ -2528,13 +2528,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>55.1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>20.2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2553,13 +2553,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>44.9</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2584,7 +2584,7 @@
         <v>27.9</v>
       </c>
       <c r="G7" t="n">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -2609,7 +2609,7 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -2653,10 +2653,10 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5083,10 +5083,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>88.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>71.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -5108,10 +5108,10 @@
         <v>76.8</v>
       </c>
       <c r="F3" t="n">
-        <v>60.4</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5133,10 +5133,10 @@
         <v>59.6</v>
       </c>
       <c r="F4" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -5158,10 +5158,10 @@
         <v>53.4</v>
       </c>
       <c r="F5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5183,10 +5183,10 @@
         <v>46.6</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5208,10 +5208,10 @@
         <v>40.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5233,10 +5233,10 @@
         <v>23.2</v>
       </c>
       <c r="F8" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5983,13 +5983,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>79.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>62.9</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>37.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6017,7 +6017,7 @@
         <v>25.5</v>
       </c>
       <c r="H3" t="n">
-        <v>11.5</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="4">
@@ -6045,7 +6045,7 @@
         <v>45.7</v>
       </c>
       <c r="H4" t="n">
-        <v>27.8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -6067,13 +6067,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>20.2</v>
+        <v>54.3</v>
       </c>
       <c r="H5" t="n">
-        <v>6.5</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6">
@@ -6092,16 +6092,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>66.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6129,7 +6129,7 @@
         <v>11.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8">
@@ -6157,7 +6157,7 @@
         <v>13.8</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="9">
@@ -6176,16 +6176,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6204,16 +6204,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>13.3</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>45.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="11">
@@ -6241,7 +6241,7 @@
         <v>0.9</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -6269,7 +6269,7 @@
         <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6316,16 +6316,16 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>33.6</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -1180,13 +1180,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>66.3</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1205,13 +1205,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1258,10 +1258,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>68.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>30.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="7">
@@ -1280,13 +1280,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>57.6</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>37.1</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>25.3</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1305,13 +1305,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1358,10 +1358,10 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2459,7 +2459,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -2478,13 +2478,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>49.3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2503,13 +2503,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2578,13 +2578,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>57.9</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>27.9</v>
+        <v>73.7</v>
       </c>
       <c r="G7" t="n">
-        <v>9.300000000000001</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="8">
@@ -2600,16 +2600,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>17.9</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>26.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9">
@@ -2675,13 +2675,13 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -3024,10 +3024,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>95.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="I2" t="n">
-        <v>65.2</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3055,10 +3055,10 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>67.8</v>
+        <v>67.3</v>
       </c>
       <c r="I3" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4">
@@ -3083,13 +3083,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>84.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>30.8</v>
+        <v>31.5</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3114,10 +3114,10 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>37.5</v>
+        <v>32.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.1</v>
@@ -3142,16 +3142,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>69.5</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>46.7</v>
+        <v>67.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -3173,13 +3173,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>50.5</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>7.2</v>
+        <v>14.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="I7" t="n">
         <v>0.1</v>
@@ -3201,16 +3201,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>76.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>43.6</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3232,19 +3232,19 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>69.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3263,16 +3263,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>30.4</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3325,13 +3325,13 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -5105,7 +5105,7 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>76.8</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
         <v>100</v>
@@ -5130,7 +5130,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>59.6</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -5155,7 +5155,7 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>53.4</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>46.6</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>40.5</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -5230,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6011,13 +6011,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>59.3</v>
+        <v>53.8</v>
       </c>
       <c r="G3" t="n">
-        <v>25.5</v>
+        <v>22.3</v>
       </c>
       <c r="H3" t="n">
-        <v>16.6</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="4">
@@ -6039,13 +6039,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>69.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>45.7</v>
+        <v>42.4</v>
       </c>
       <c r="H4" t="n">
-        <v>34</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="5">
@@ -6073,7 +6073,7 @@
         <v>54.3</v>
       </c>
       <c r="H5" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="6">
@@ -6120,16 +6120,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>66.5</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>22.8</v>
+        <v>34.6</v>
       </c>
       <c r="G7" t="n">
-        <v>11.8</v>
+        <v>17.7</v>
       </c>
       <c r="H7" t="n">
-        <v>7.1</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="8">
@@ -6148,16 +6148,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>76.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>35.1</v>
+        <v>46.2</v>
       </c>
       <c r="G8" t="n">
-        <v>13.8</v>
+        <v>17.7</v>
       </c>
       <c r="H8" t="n">
-        <v>8.9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="9">
@@ -6213,7 +6213,7 @@
         <v>45.7</v>
       </c>
       <c r="H10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -6232,16 +6232,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -6260,16 +6260,16 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -1853,13 +1853,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>53.8</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1881,13 +1881,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>65.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>42.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>31.5</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="5">
@@ -1915,7 +1915,7 @@
         <v>54.3</v>
       </c>
       <c r="H5" t="n">
-        <v>16.7</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="6">
@@ -1965,13 +1965,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>34.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1993,13 +1993,13 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>17.7</v>
+        <v>34.1</v>
       </c>
       <c r="H8" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2055,7 +2055,7 @@
         <v>45.7</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="11">
@@ -2987,7 +2987,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>60.4</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="3">
@@ -3034,10 +3034,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>63.5</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>28.7</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="5">
@@ -3134,10 +3134,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6439,10 +6439,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>79.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="3">
@@ -6464,10 +6464,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="G3" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="4">
@@ -6486,13 +6486,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>73.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="F4" t="n">
-        <v>17.2</v>
+        <v>16.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5">
@@ -6511,13 +6511,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>58.6</v>
+        <v>54</v>
       </c>
       <c r="F5" t="n">
-        <v>13.8</v>
+        <v>12.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -6533,16 +6533,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>32.8</v>
+        <v>46</v>
       </c>
       <c r="F6" t="n">
-        <v>6.1</v>
+        <v>8.6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -6558,16 +6558,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>63.5</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>19.8</v>
+        <v>31.2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Houston Chr</t>
+          <t>Northwestern LA</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6601,23 +6601,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Northwestern LA</t>
+          <t>Houston Chr</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6693,7 +6693,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>88.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -6743,7 +6743,7 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6993,7 +6993,7 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>67.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -7024,10 +7024,10 @@
         <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>64.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7296,10 +7296,10 @@
         <v>100</v>
       </c>
       <c r="I11" t="n">
-        <v>35.4</v>
+        <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>8.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="12">
@@ -8478,10 +8478,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>95.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>64.90000000000001</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="3">
@@ -8509,10 +8509,10 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>67.3</v>
+        <v>63.2</v>
       </c>
       <c r="I3" t="n">
-        <v>25.2</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="4">
@@ -8537,13 +8537,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>85.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>31.5</v>
+        <v>36.8</v>
       </c>
       <c r="I4" t="n">
-        <v>9.199999999999999</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="5">
@@ -8568,13 +8568,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>32.7</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -8599,13 +8599,13 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>67.3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8630,13 +8630,13 @@
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -10295,13 +10295,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>66.3</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>32.8</v>
+        <v>49.9</v>
       </c>
       <c r="G2" t="n">
-        <v>17.4</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="3">
@@ -10320,13 +10320,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -10348,10 +10348,10 @@
         <v>55.4</v>
       </c>
       <c r="F4" t="n">
-        <v>25.5</v>
+        <v>28.4</v>
       </c>
       <c r="G4" t="n">
-        <v>12.4</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="5">
@@ -10373,10 +10373,10 @@
         <v>31.9</v>
       </c>
       <c r="F5" t="n">
-        <v>15.6</v>
+        <v>13.2</v>
       </c>
       <c r="G5" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="6">
@@ -10398,10 +10398,10 @@
         <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>41.2</v>
+        <v>36.9</v>
       </c>
       <c r="G6" t="n">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="7">
@@ -10423,10 +10423,10 @@
         <v>44.6</v>
       </c>
       <c r="F7" t="n">
-        <v>17.4</v>
+        <v>20.5</v>
       </c>
       <c r="G7" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="8">
@@ -10445,13 +10445,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>40.7</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>20.6</v>
+        <v>51.1</v>
       </c>
       <c r="G8" t="n">
-        <v>9.699999999999999</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="9">
@@ -10495,13 +10495,13 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>33.7</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -963,13 +963,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>76.8</v>
+        <v>79.3</v>
       </c>
       <c r="H2" t="n">
-        <v>47.7</v>
+        <v>51.4</v>
       </c>
       <c r="I2" t="n">
-        <v>32.8</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="3">
@@ -994,13 +994,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>43.5</v>
+        <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>17.9</v>
+        <v>20.9</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4">
@@ -1025,13 +1025,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>43.2</v>
+        <v>41.9</v>
       </c>
       <c r="I4" t="n">
-        <v>18.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="5">
@@ -1056,13 +1056,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>76.3</v>
+        <v>72.2</v>
       </c>
       <c r="H5" t="n">
-        <v>38.1</v>
+        <v>34.8</v>
       </c>
       <c r="I5" t="n">
-        <v>22.8</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="6">
@@ -1087,13 +1087,13 @@
         <v>74.2</v>
       </c>
       <c r="G6" t="n">
-        <v>20.9</v>
+        <v>24.1</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -1146,16 +1146,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="G8" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="H8" t="n">
-        <v>29.6</v>
+        <v>27.7</v>
       </c>
       <c r="I8" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="9">
@@ -1177,13 +1177,13 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="G9" t="n">
-        <v>11.5</v>
+        <v>9.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1205,19 +1205,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>79.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F10" t="n">
-        <v>44.2</v>
+        <v>43.6</v>
       </c>
       <c r="G10" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="11">
@@ -1236,13 +1236,13 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>69.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F11" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
         <v>1.1</v>
@@ -1273,10 +1273,10 @@
         <v>18.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I12" t="n">
         <v>0.1</v>
@@ -1304,10 +1304,10 @@
         <v>15.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I13" t="n">
         <v>0.1</v>
@@ -1388,13 +1388,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>68.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>22.6</v>
+        <v>24.2</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
         <v>0.6</v>
@@ -1453,10 +1453,10 @@
         <v>35.3</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -1481,13 +1481,13 @@
         <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>31.8</v>
+        <v>27.2</v>
       </c>
       <c r="E19" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -1887,7 +1887,7 @@
         <v>65.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>48.9</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="5">
@@ -1915,7 +1915,7 @@
         <v>54.3</v>
       </c>
       <c r="H5" t="n">
-        <v>15.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="6">
@@ -6141,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -6263,10 +6263,10 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>73.7</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>25.1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -6288,10 +6288,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7908,10 +7908,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>77.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>47.6</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="3">
@@ -7939,7 +7939,7 @@
         <v>62.7</v>
       </c>
       <c r="H3" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="4">
@@ -7961,13 +7961,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>29.3</v>
       </c>
       <c r="H4" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
@@ -7989,13 +7989,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>56.8</v>
+        <v>54.5</v>
       </c>
       <c r="G5" t="n">
-        <v>14.1</v>
+        <v>11.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -8042,13 +8042,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>66.5</v>
+        <v>67.5</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H7" t="n">
         <v>2.2</v>
@@ -8070,16 +8070,16 @@
         <v>42.8</v>
       </c>
       <c r="E8" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8101,13 +8101,13 @@
         <v>39.7</v>
       </c>
       <c r="F9" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -8129,7 +8129,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
         <v>0.3</v>
@@ -8481,7 +8481,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>66.3</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="3">
@@ -8543,7 +8543,7 @@
         <v>36.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -6141,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>66</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="3">
@@ -6263,10 +6263,10 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>100</v>
+        <v>73.7</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="8">
@@ -6288,10 +6288,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="9">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -4509,10 +4509,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>59.6</v>
+        <v>61.1</v>
       </c>
       <c r="G2" t="n">
-        <v>39.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -4534,10 +4534,10 @@
         <v>74.5</v>
       </c>
       <c r="F3" t="n">
-        <v>39.2</v>
+        <v>37.4</v>
       </c>
       <c r="G3" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="4">
@@ -4556,13 +4556,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>67.5</v>
+        <v>60.8</v>
       </c>
       <c r="F4" t="n">
-        <v>39.6</v>
+        <v>35.5</v>
       </c>
       <c r="G4" t="n">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="5">
@@ -4581,13 +4581,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>45.7</v>
+        <v>53.2</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3</v>
+        <v>16.8</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="6">
@@ -4596,23 +4596,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boise St</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>99</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>54.3</v>
+        <v>46.7</v>
       </c>
       <c r="F6" t="n">
-        <v>20.3</v>
+        <v>15.6</v>
       </c>
       <c r="G6" t="n">
-        <v>10.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Boise St</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4631,13 +4631,13 @@
         <v>88.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>31.2</v>
+        <v>38</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -4659,7 +4659,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="G8" t="n">
         <v>2.1</v>
@@ -4684,7 +4684,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>0.9</v>
@@ -4709,10 +4709,10 @@
         <v>10.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -4737,7 +4737,7 @@
         <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -4778,10 +4778,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -507,13 +507,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="G2" t="n">
-        <v>54.6</v>
+        <v>53.3</v>
       </c>
       <c r="H2" t="n">
-        <v>35.2</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="3">
@@ -541,7 +541,7 @@
         <v>63.1</v>
       </c>
       <c r="H3" t="n">
-        <v>35.5</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="4">
@@ -563,13 +563,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>48.8</v>
+        <v>50.5</v>
       </c>
       <c r="G4" t="n">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>60.9</v>
+        <v>58.8</v>
       </c>
       <c r="G5" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="6">
@@ -616,16 +616,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>72.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>32.7</v>
+        <v>35.7</v>
       </c>
       <c r="G6" t="n">
-        <v>10.6</v>
+        <v>12.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="7">
@@ -644,16 +644,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>69.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="G7" t="n">
         <v>12.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -672,16 +672,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -700,13 +700,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>24.9</v>
+        <v>27.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
@@ -728,16 +728,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>75.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="F10" t="n">
-        <v>20.8</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="11">
@@ -756,7 +756,7 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="F11" t="n">
         <v>8.699999999999999</v>
@@ -781,16 +781,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>81.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
-        <v>28.2</v>
+        <v>26.4</v>
       </c>
       <c r="F12" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
         <v>0.4</v>
@@ -809,10 +809,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>33.2</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>0.7</v>
@@ -837,19 +837,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="E14" t="n">
-        <v>22.1</v>
+        <v>18.4</v>
       </c>
       <c r="F14" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +865,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>18.6</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -963,13 +963,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>51.4</v>
+        <v>50.4</v>
       </c>
       <c r="I2" t="n">
-        <v>35.4</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="3">
@@ -997,7 +997,7 @@
         <v>43.9</v>
       </c>
       <c r="H3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="I3" t="n">
         <v>7.1</v>
@@ -1025,13 +1025,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="H4" t="n">
         <v>41.9</v>
       </c>
       <c r="I4" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="5">
@@ -1056,13 +1056,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>72.2</v>
+        <v>72.5</v>
       </c>
       <c r="H5" t="n">
-        <v>34.8</v>
+        <v>34.9</v>
       </c>
       <c r="I5" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="6">
@@ -1084,16 +1084,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>74.2</v>
+        <v>74.8</v>
       </c>
       <c r="G6" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="H6" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -1115,16 +1115,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>76.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="H7" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -1146,16 +1146,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="G8" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="H8" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="I8" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="9">
@@ -1177,16 +1177,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>51.1</v>
+        <v>52.3</v>
       </c>
       <c r="G9" t="n">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -1205,19 +1205,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>78.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10.2</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -1236,13 +1236,13 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="F11" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H11" t="n">
         <v>1.1</v>
@@ -1270,13 +1270,13 @@
         <v>66.8</v>
       </c>
       <c r="F12" t="n">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I12" t="n">
         <v>0.1</v>
@@ -1298,13 +1298,13 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>57</v>
+        <v>57.6</v>
       </c>
       <c r="F13" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H13" t="n">
         <v>0.4</v>
@@ -1329,10 +1329,10 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>43</v>
+        <v>42.4</v>
       </c>
       <c r="F14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.2</v>
@@ -1453,10 +1453,10 @@
         <v>35.3</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="n">
         <v>0.1</v>
@@ -1484,10 +1484,10 @@
         <v>27.2</v>
       </c>
       <c r="E19" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G19" t="n">
         <v>0.1</v>
@@ -1569,10 +1569,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>59.6</v>
+        <v>59.7</v>
       </c>
       <c r="G2" t="n">
-        <v>32.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1594,10 +1594,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>62.2</v>
+        <v>61.7</v>
       </c>
       <c r="G3" t="n">
-        <v>33.5</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="4">
@@ -1616,13 +1616,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="F4" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="5">
@@ -1641,13 +1641,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
         <v>14.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="6">
@@ -1663,16 +1663,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>74.5</v>
+        <v>73.2</v>
       </c>
       <c r="E6" t="n">
-        <v>48.3</v>
+        <v>47.4</v>
       </c>
       <c r="F6" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="7">
@@ -1691,13 +1691,13 @@
         <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="F7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -1719,10 +1719,10 @@
         <v>35.9</v>
       </c>
       <c r="F8" t="n">
-        <v>15.2</v>
+        <v>15.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
@@ -1738,16 +1738,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>25.5</v>
+        <v>26.8</v>
       </c>
       <c r="E9" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +1887,7 @@
         <v>65.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="5">
@@ -1912,10 +1912,10 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>54.3</v>
+        <v>48.9</v>
       </c>
       <c r="H5" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="6">
@@ -1999,7 +1999,7 @@
         <v>34.1</v>
       </c>
       <c r="H8" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="9">
@@ -2052,10 +2052,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="H10" t="n">
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="11">
@@ -2237,13 +2237,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>79.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="F2" t="n">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="G2" t="n">
-        <v>33.7</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="3">
@@ -2262,13 +2262,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>71.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>44.8</v>
+        <v>45.1</v>
       </c>
       <c r="G3" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -2287,13 +2287,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>57.6</v>
       </c>
       <c r="F4" t="n">
-        <v>33.1</v>
+        <v>26.7</v>
       </c>
       <c r="G4" t="n">
-        <v>15.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="5">
@@ -2312,13 +2312,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>47.4</v>
+        <v>57.4</v>
       </c>
       <c r="F5" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="6">
@@ -2337,13 +2337,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>52.6</v>
+        <v>42.6</v>
       </c>
       <c r="F6" t="n">
-        <v>20.2</v>
+        <v>16.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7">
@@ -2362,13 +2362,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>33</v>
+        <v>42.4</v>
       </c>
       <c r="F7" t="n">
-        <v>9.9</v>
+        <v>15.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="8">
@@ -2384,13 +2384,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>42.2</v>
+        <v>40.4</v>
       </c>
       <c r="E8" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="F8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G8" t="n">
         <v>1.2</v>
@@ -2415,7 +2415,7 @@
         <v>10.3</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
@@ -2437,13 +2437,13 @@
         <v>55.1</v>
       </c>
       <c r="E10" t="n">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="F10" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="11">
@@ -2459,16 +2459,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>57.8</v>
+        <v>59.6</v>
       </c>
       <c r="E11" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="F11" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -2566,10 +2566,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>73.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="4">
@@ -2591,10 +2591,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>26.1</v>
+        <v>26.9</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -2694,7 +2694,7 @@
         <v>41.1</v>
       </c>
       <c r="G8" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2851,10 +2851,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>74.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>58.7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -2873,7 +2873,7 @@
         <v>50.8</v>
       </c>
       <c r="E3" t="n">
-        <v>13.2</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="4">
@@ -2892,7 +2892,7 @@
         <v>49.2</v>
       </c>
       <c r="E4" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="5">
@@ -2908,10 +2908,10 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="E5" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
     </row>
   </sheetData>
@@ -3299,10 +3299,10 @@
         <v>57</v>
       </c>
       <c r="E3" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="4">
@@ -3321,10 +3321,10 @@
         <v>47.1</v>
       </c>
       <c r="E4" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
@@ -3346,7 +3346,7 @@
         <v>16.4</v>
       </c>
       <c r="F5" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -3387,7 +3387,7 @@
         <v>52.9</v>
       </c>
       <c r="E7" t="n">
-        <v>30.1</v>
+        <v>29.6</v>
       </c>
       <c r="F7" t="n">
         <v>4.9</v>
@@ -3409,10 +3409,10 @@
         <v>43</v>
       </c>
       <c r="E8" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
   </sheetData>
@@ -3477,10 +3477,10 @@
         <v>83.3</v>
       </c>
       <c r="E2" t="n">
-        <v>60.7</v>
+        <v>57.8</v>
       </c>
       <c r="F2" t="n">
-        <v>27.3</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="3">
@@ -3496,13 +3496,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>91.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>75</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>53.7</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="4">
@@ -3521,10 +3521,10 @@
         <v>73.40000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>17.4</v>
+        <v>16.5</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -3540,13 +3540,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>56.6</v>
+        <v>57.1</v>
       </c>
       <c r="E5" t="n">
-        <v>20.2</v>
+        <v>22.7</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -3562,10 +3562,10 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>43.4</v>
+        <v>42.9</v>
       </c>
       <c r="E6" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="F6" t="n">
         <v>3.9</v>
@@ -3587,10 +3587,10 @@
         <v>26.6</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -3606,13 +3606,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -4038,13 +4038,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>93.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>82.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>69</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="3">
@@ -4066,13 +4066,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>69.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="H3" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="4">
@@ -4097,10 +4097,10 @@
         <v>38.1</v>
       </c>
       <c r="G4" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4122,10 +4122,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>62.9</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="H5" t="n">
         <v>5.1</v>
@@ -4147,16 +4147,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="F6" t="n">
         <v>25.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="7">
@@ -4181,10 +4181,10 @@
         <v>51.9</v>
       </c>
       <c r="G7" t="n">
-        <v>30.6</v>
+        <v>31.2</v>
       </c>
       <c r="H7" t="n">
-        <v>8.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -4206,13 +4206,13 @@
         <v>61.3</v>
       </c>
       <c r="F8" t="n">
-        <v>21.9</v>
+        <v>20.2</v>
       </c>
       <c r="G8" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -4231,16 +4231,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>57.4</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -4259,10 +4259,10 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>42.6</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
         <v>0.8</v>
@@ -4296,7 +4296,7 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -4321,10 +4321,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -4349,7 +4349,7 @@
         <v>7.4</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H13" t="n">
         <v>0.4</v>
@@ -4371,7 +4371,7 @@
         <v>44.5</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="F14" t="n">
         <v>4.4</v>
@@ -4506,13 +4506,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>81.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>61.1</v>
+        <v>56.2</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="3">
@@ -4531,13 +4531,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>74.5</v>
+        <v>72.8</v>
       </c>
       <c r="F3" t="n">
-        <v>37.4</v>
+        <v>35.2</v>
       </c>
       <c r="G3" t="n">
-        <v>17.3</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="4">
@@ -4556,13 +4556,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>60.8</v>
+        <v>58.4</v>
       </c>
       <c r="F4" t="n">
-        <v>35.5</v>
+        <v>34.2</v>
       </c>
       <c r="G4" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="5">
@@ -4581,13 +4581,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>53.2</v>
+        <v>55.2</v>
       </c>
       <c r="F5" t="n">
-        <v>16.8</v>
+        <v>19.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4606,13 +4606,13 @@
         <v>96.59999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>46.7</v>
+        <v>44.6</v>
       </c>
       <c r="F6" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="7">
@@ -4631,13 +4631,13 @@
         <v>88.40000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>38</v>
+        <v>40.3</v>
       </c>
       <c r="F7" t="n">
-        <v>19.3</v>
+        <v>22.2</v>
       </c>
       <c r="G7" t="n">
-        <v>8.199999999999999</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="8">
@@ -4656,13 +4656,13 @@
         <v>72.7</v>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="F8" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -4678,16 +4678,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>45.4</v>
+        <v>50.2</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>11.9</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -4703,16 +4703,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>54.6</v>
+        <v>49.8</v>
       </c>
       <c r="E10" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -4855,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="3">
@@ -4899,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="5">
@@ -5642,10 +5642,10 @@
         <v>82.2</v>
       </c>
       <c r="G2" t="n">
-        <v>59.5</v>
+        <v>57.5</v>
       </c>
       <c r="H2" t="n">
-        <v>38.9</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="3">
@@ -5667,13 +5667,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>69.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>43.8</v>
+        <v>43.1</v>
       </c>
       <c r="H3" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="4">
@@ -5698,10 +5698,10 @@
         <v>68.8</v>
       </c>
       <c r="G4" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="H4" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="5">
@@ -5723,13 +5723,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>52.5</v>
+        <v>52.3</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="6">
@@ -5748,16 +5748,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>63.9</v>
+        <v>67.8</v>
       </c>
       <c r="F6" t="n">
-        <v>33.7</v>
+        <v>35.9</v>
       </c>
       <c r="G6" t="n">
-        <v>11.6</v>
+        <v>12.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7">
@@ -5782,10 +5782,10 @@
         <v>21.3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
@@ -5804,16 +5804,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>60.1</v>
+        <v>61.7</v>
       </c>
       <c r="F8" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9">
@@ -5838,10 +5838,10 @@
         <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="10">
@@ -5866,10 +5866,10 @@
         <v>11.8</v>
       </c>
       <c r="G10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -5888,16 +5888,16 @@
         <v>73.09999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>32.3</v>
+        <v>30.9</v>
       </c>
       <c r="F11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="12">
@@ -5922,7 +5922,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="n">
         <v>0.7</v>
@@ -5944,16 +5944,16 @@
         <v>80.5</v>
       </c>
       <c r="E13" t="n">
-        <v>33.3</v>
+        <v>29.6</v>
       </c>
       <c r="F13" t="n">
-        <v>13.3</v>
+        <v>11.7</v>
       </c>
       <c r="G13" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
@@ -5972,10 +5972,10 @@
         <v>19.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -6028,7 +6028,7 @@
         <v>26.9</v>
       </c>
       <c r="E16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="F16" t="n">
         <v>1.8</v>
@@ -6141,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -6266,7 +6266,7 @@
         <v>73.7</v>
       </c>
       <c r="G7" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="8">
@@ -6993,7 +6993,7 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>75.59999999999999</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -7299,7 +7299,7 @@
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>24.4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -7513,13 +7513,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>67.2</v>
+        <v>66.3</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>43.3</v>
       </c>
       <c r="H2" t="n">
-        <v>29</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="3">
@@ -7544,10 +7544,10 @@
         <v>55.5</v>
       </c>
       <c r="G3" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4">
@@ -7575,7 +7575,7 @@
         <v>45.7</v>
       </c>
       <c r="H4" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="5">
@@ -7597,13 +7597,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>53.6</v>
+        <v>46.3</v>
       </c>
       <c r="G5" t="n">
-        <v>21.1</v>
+        <v>17.3</v>
       </c>
       <c r="H5" t="n">
-        <v>10.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -7625,13 +7625,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
       <c r="G6" t="n">
-        <v>18.5</v>
+        <v>22.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8.300000000000001</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="7">
@@ -7656,10 +7656,10 @@
         <v>31.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13.2</v>
+        <v>13.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="8">
@@ -7684,7 +7684,7 @@
         <v>14.3</v>
       </c>
       <c r="G8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H8" t="n">
         <v>1.3</v>
@@ -7706,16 +7706,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>53.8</v>
+        <v>61.6</v>
       </c>
       <c r="F9" t="n">
-        <v>16.8</v>
+        <v>20.3</v>
       </c>
       <c r="G9" t="n">
-        <v>8.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="10">
@@ -7740,10 +7740,10 @@
         <v>29.1</v>
       </c>
       <c r="G10" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="11">
@@ -7759,19 +7759,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>71.8</v>
+        <v>67.5</v>
       </c>
       <c r="E11" t="n">
-        <v>36.8</v>
+        <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>13.7</v>
+        <v>10.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -7787,16 +7787,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>28.2</v>
+        <v>32.5</v>
       </c>
       <c r="E12" t="n">
         <v>9.4</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H12" t="n">
         <v>0.2</v>
@@ -7911,7 +7911,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>49.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -7936,10 +7936,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>62.7</v>
+        <v>62.9</v>
       </c>
       <c r="H3" t="n">
-        <v>31.2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -7961,13 +7961,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="H4" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="5">
@@ -7989,13 +7989,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>54.5</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>11.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="6">
@@ -8014,16 +8014,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>52.1</v>
+        <v>53.3</v>
       </c>
       <c r="F6" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7">
@@ -8042,16 +8042,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="F7" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="G7" t="n">
         <v>6.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -8067,16 +8067,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>42.8</v>
+        <v>35.6</v>
       </c>
       <c r="E8" t="n">
-        <v>13.3</v>
+        <v>11.4</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -8095,19 +8095,19 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>71.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>39.7</v>
+        <v>39.2</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="G9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -8123,13 +8123,13 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>28.1</v>
+        <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G10" t="n">
         <v>0.3</v>
@@ -8151,16 +8151,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>57.2</v>
+        <v>64.3</v>
       </c>
       <c r="E11" t="n">
-        <v>19.2</v>
+        <v>21.3</v>
       </c>
       <c r="F11" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
@@ -8236,10 +8236,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>78.5</v>
+        <v>77.5</v>
       </c>
       <c r="G2" t="n">
-        <v>47.8</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="3">
@@ -8261,10 +8261,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>76.8</v>
+        <v>79.5</v>
       </c>
       <c r="G3" t="n">
-        <v>38.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="4">
@@ -8283,13 +8283,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>59.8</v>
+        <v>59.6</v>
       </c>
       <c r="F4" t="n">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -8308,13 +8308,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>71.90000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>19.4</v>
+        <v>20.4</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6">
@@ -8333,13 +8333,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="F6" t="n">
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -8355,16 +8355,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>45.9</v>
+        <v>43.1</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -8380,16 +8380,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>54.1</v>
+        <v>56.9</v>
       </c>
       <c r="E8" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8481,7 +8481,7 @@
         <v>97.40000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>67.3</v>
+        <v>67.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -8512,7 +8512,7 @@
         <v>63.2</v>
       </c>
       <c r="I3" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -8887,10 +8887,10 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>74.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>43.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="3">
@@ -8909,10 +8909,10 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>74.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>41.4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -8931,10 +8931,10 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>25.3</v>
+        <v>19.4</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5">
@@ -8953,10 +8953,10 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>25.6</v>
+        <v>23.4</v>
       </c>
       <c r="F5" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -9473,13 +9473,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>86.2</v>
+        <v>86</v>
       </c>
       <c r="G2" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="H2" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="3">
@@ -9501,13 +9501,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>77.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="G3" t="n">
-        <v>56.1</v>
+        <v>56.5</v>
       </c>
       <c r="H3" t="n">
-        <v>28.1</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="4">
@@ -9529,7 +9529,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="G4" t="n">
         <v>26.1</v>
@@ -9557,13 +9557,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>53.3</v>
+        <v>51.1</v>
       </c>
       <c r="G5" t="n">
-        <v>18.4</v>
+        <v>17.3</v>
       </c>
       <c r="H5" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -9582,16 +9582,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>78.2</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>41.9</v>
+        <v>43.6</v>
       </c>
       <c r="G6" t="n">
-        <v>16.6</v>
+        <v>17.2</v>
       </c>
       <c r="H6" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -9638,13 +9638,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>33.5</v>
+        <v>37.9</v>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
         <v>0.4</v>
@@ -9666,10 +9666,10 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>54.1</v>
+        <v>52.3</v>
       </c>
       <c r="F9" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
@@ -9691,19 +9691,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>80.3</v>
+        <v>80.8</v>
       </c>
       <c r="E10" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -9719,19 +9719,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>82.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>16.2</v>
+        <v>14.6</v>
       </c>
       <c r="G11" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -9753,10 +9753,10 @@
         <v>15.7</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
@@ -9781,10 +9781,10 @@
         <v>6.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -9806,10 +9806,10 @@
         <v>63.8</v>
       </c>
       <c r="E14" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0.9</v>
@@ -9859,13 +9859,13 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>19.3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
         <v>0.2</v>
@@ -9887,10 +9887,10 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="F17" t="n">
         <v>0.2</v>
@@ -9975,7 +9975,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>34.4</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="3">
@@ -9994,13 +9994,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>85.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>63.4</v>
       </c>
       <c r="G3" t="n">
-        <v>42.5</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="4">
@@ -10019,13 +10019,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>76.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="F4" t="n">
-        <v>25.7</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="5">
@@ -10044,13 +10044,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>57.1</v>
+        <v>56.4</v>
       </c>
       <c r="F5" t="n">
         <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
@@ -10069,13 +10069,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>42.9</v>
+        <v>43.6</v>
       </c>
       <c r="F6" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -10091,16 +10091,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>45.1</v>
+        <v>41.9</v>
       </c>
       <c r="E7" t="n">
-        <v>10.1</v>
+        <v>7.5</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
@@ -10116,16 +10116,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>53.4</v>
+        <v>55.6</v>
       </c>
       <c r="E8" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -10141,16 +10141,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>46.5</v>
+        <v>53.8</v>
       </c>
       <c r="E9" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
@@ -10166,16 +10166,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>53.5</v>
+        <v>46.2</v>
       </c>
       <c r="E10" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="F10" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11">
@@ -10191,16 +10191,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>46.6</v>
+        <v>44.4</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12">
@@ -10216,16 +10216,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>54.9</v>
+        <v>58.1</v>
       </c>
       <c r="E12" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -10298,10 +10298,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>49.9</v>
+        <v>51.1</v>
       </c>
       <c r="G2" t="n">
-        <v>27.7</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="3">
@@ -10348,10 +10348,10 @@
         <v>55.4</v>
       </c>
       <c r="F4" t="n">
-        <v>28.4</v>
+        <v>23.8</v>
       </c>
       <c r="G4" t="n">
-        <v>13.1</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="5">
@@ -10370,13 +10370,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>31.9</v>
+        <v>29.7</v>
       </c>
       <c r="F5" t="n">
-        <v>13.2</v>
+        <v>10.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="6">
@@ -10395,13 +10395,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>70.3</v>
       </c>
       <c r="F6" t="n">
-        <v>36.9</v>
+        <v>38.2</v>
       </c>
       <c r="G6" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="7">
@@ -10423,10 +10423,10 @@
         <v>44.6</v>
       </c>
       <c r="F7" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8">
@@ -10448,10 +10448,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>51.1</v>
+        <v>57.6</v>
       </c>
       <c r="G8" t="n">
-        <v>22.8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -7908,10 +7908,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="3">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tulsa</t>
+          <t>Wichita St</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -7936,10 +7936,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>62.9</v>
+        <v>48.4</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wichita St</t>
+          <t>Tulsa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -7961,13 +7961,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="G4" t="n">
-        <v>29.2</v>
+        <v>43.8</v>
       </c>
       <c r="H4" t="n">
-        <v>11.4</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="5">
@@ -7989,13 +7989,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>60.1</v>
       </c>
       <c r="G5" t="n">
-        <v>11.9</v>
+        <v>13.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -8014,16 +8014,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>53.3</v>
+        <v>34.5</v>
       </c>
       <c r="F6" t="n">
-        <v>23.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FL Atlantic</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -8042,16 +8042,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>67.3</v>
+        <v>49.9</v>
       </c>
       <c r="F7" t="n">
-        <v>24.3</v>
+        <v>12.3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.9</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -8060,26 +8060,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>FL Atlantic</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>35.6</v>
+        <v>65.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.4</v>
+        <v>35.1</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>10.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -8098,16 +8098,16 @@
         <v>74</v>
       </c>
       <c r="E9" t="n">
-        <v>39.2</v>
+        <v>53.5</v>
       </c>
       <c r="F9" t="n">
-        <v>19.6</v>
+        <v>27.1</v>
       </c>
       <c r="G9" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -8126,16 +8126,16 @@
         <v>26</v>
       </c>
       <c r="E10" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -8151,16 +8151,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>34.3</v>
       </c>
       <c r="E11" t="n">
-        <v>21.3</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -2240,10 +2240,10 @@
         <v>77.3</v>
       </c>
       <c r="F2" t="n">
-        <v>52.5</v>
+        <v>51.9</v>
       </c>
       <c r="G2" t="n">
-        <v>32.5</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="3">
@@ -2265,10 +2265,10 @@
         <v>70.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>45.1</v>
+        <v>42.9</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="4">
@@ -2287,13 +2287,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>57.6</v>
+        <v>56.9</v>
       </c>
       <c r="F4" t="n">
-        <v>26.7</v>
+        <v>26.3</v>
       </c>
       <c r="G4" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="5">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MTSU</t>
+          <t>Louisiana Tech</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2312,13 +2312,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>57.4</v>
+        <v>36.6</v>
       </c>
       <c r="F5" t="n">
-        <v>23.4</v>
+        <v>13.7</v>
       </c>
       <c r="G5" t="n">
-        <v>10.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kennesaw</t>
+          <t>MTSU</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2337,13 +2337,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>42.6</v>
+        <v>63.3</v>
       </c>
       <c r="F6" t="n">
-        <v>16.1</v>
+        <v>25.9</v>
       </c>
       <c r="G6" t="n">
-        <v>7.1</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="7">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louisiana Tech</t>
+          <t>Kennesaw</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2362,13 +2362,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>42.4</v>
+        <v>43.1</v>
       </c>
       <c r="F7" t="n">
-        <v>15.5</v>
+        <v>18.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8">
@@ -2390,10 +2390,10 @@
         <v>10.4</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -2402,23 +2402,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Missouri St</t>
+          <t>Florida Intl</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>44.9</v>
+        <v>55.7</v>
       </c>
       <c r="E9" t="n">
-        <v>10.3</v>
+        <v>12.7</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
@@ -2427,23 +2427,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Florida Intl</t>
+          <t>Missouri St</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>55.1</v>
+        <v>44.3</v>
       </c>
       <c r="E10" t="n">
-        <v>12.4</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -2465,10 +2465,10 @@
         <v>18.6</v>
       </c>
       <c r="F11" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -1884,10 +1884,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>65.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>49.8</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="5">
@@ -1912,10 +1912,10 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>48.9</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>12.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="6">
@@ -1996,10 +1996,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>34.1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>22.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2052,10 +2052,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>51.1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2541,10 +2541,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>58.9</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>30.2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -2566,10 +2566,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>73.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>43.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2591,10 +2591,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>26.9</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -2691,10 +2691,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>41.1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6141,7 +6141,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>70.09999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6263,10 +6263,10 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>73.7</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>25.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -6288,10 +6288,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>26.3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6439,10 +6439,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>78.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="G2" t="n">
-        <v>31.9</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="3">
@@ -6464,10 +6464,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>80.2</v>
+        <v>76.5</v>
       </c>
       <c r="G3" t="n">
-        <v>57.7</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="4">
@@ -6486,13 +6486,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>68.8</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>16.1</v>
+        <v>23.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -6511,13 +6511,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>12.8</v>
+        <v>23.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6536,13 +6536,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6561,13 +6561,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6993,7 +6993,7 @@
         <v>100</v>
       </c>
       <c r="J2" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -7299,7 +7299,7 @@
         <v>100</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7513,13 +7513,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>66.3</v>
+        <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>43.3</v>
+        <v>45.1</v>
       </c>
       <c r="H2" t="n">
-        <v>27.7</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="3">
@@ -7541,13 +7541,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>55.5</v>
+        <v>51.8</v>
       </c>
       <c r="G3" t="n">
-        <v>23.6</v>
+        <v>21.9</v>
       </c>
       <c r="H3" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -7572,10 +7572,10 @@
         <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="H4" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="5">
@@ -7600,10 +7600,10 @@
         <v>46.3</v>
       </c>
       <c r="G5" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="H5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -7628,10 +7628,10 @@
         <v>53.7</v>
       </c>
       <c r="G6" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="H6" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -7656,10 +7656,10 @@
         <v>31.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="8">
@@ -7678,16 +7678,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>41.6</v>
+        <v>34.1</v>
       </c>
       <c r="F8" t="n">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7706,16 +7706,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>61.6</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>20.3</v>
+        <v>23.9</v>
       </c>
       <c r="G9" t="n">
-        <v>10.7</v>
+        <v>12.4</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="10">
@@ -7731,19 +7731,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>80.5</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>52.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1</v>
+        <v>36.5</v>
       </c>
       <c r="G10" t="n">
-        <v>12.3</v>
+        <v>15.5</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="11">
@@ -7759,19 +7759,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>67.5</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7787,19 +7787,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>32.5</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4</v>
+        <v>28.1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -7815,16 +7815,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -8478,10 +8478,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>67.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -8509,10 +8509,10 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>63.2</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -8540,10 +8540,10 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>36.8</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>9.4</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="5">
@@ -8571,10 +8571,10 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -10298,10 +10298,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>51.1</v>
+        <v>63.6</v>
       </c>
       <c r="G2" t="n">
-        <v>29.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -10345,13 +10345,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>55.4</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>23.8</v>
+        <v>42.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.2</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="5">
@@ -10370,13 +10370,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>29.7</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7</v>
+        <v>36.4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="6">
@@ -10395,13 +10395,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>70.3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -10420,13 +10420,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>44.6</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -10448,10 +10448,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>57.6</v>
+        <v>57.2</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>29.3</v>
       </c>
     </row>
     <row r="9">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -1887,7 +1887,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>77.2</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1915,7 +1915,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>22.8</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="6">
@@ -6442,7 +6442,7 @@
         <v>76.7</v>
       </c>
       <c r="G2" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="3">
@@ -6492,7 +6492,7 @@
         <v>23.5</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -7516,7 +7516,7 @@
         <v>69</v>
       </c>
       <c r="G2" t="n">
-        <v>45.1</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
         <v>28.7</v>
@@ -7628,7 +7628,7 @@
         <v>53.7</v>
       </c>
       <c r="G6" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
         <v>10</v>
@@ -7656,10 +7656,10 @@
         <v>31.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -7687,7 +7687,7 @@
         <v>3.6</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -7706,16 +7706,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>71.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F9" t="n">
-        <v>23.9</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="10">
@@ -7740,10 +7740,10 @@
         <v>36.5</v>
       </c>
       <c r="G10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="11">
@@ -7790,16 +7790,16 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>28.1</v>
+        <v>30.5</v>
       </c>
       <c r="F12" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -8481,7 +8481,7 @@
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>76.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -8543,7 +8543,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>23.6</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="5">
@@ -10298,10 +10298,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="3">
@@ -10373,7 +10373,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="G5" t="n">
         <v>14.1</v>
@@ -10451,7 +10451,7 @@
         <v>57.2</v>
       </c>
       <c r="G8" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="9">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -994,7 +994,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="H3" t="n">
         <v>20.8</v>
@@ -1062,7 +1062,7 @@
         <v>34.9</v>
       </c>
       <c r="I5" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="6">
@@ -1146,16 +1146,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>80.5</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="H8" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="I8" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="9">
@@ -1177,16 +1177,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>52.3</v>
+        <v>52.7</v>
       </c>
       <c r="G9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="10">
@@ -1205,16 +1205,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>79.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="F10" t="n">
-        <v>42.5</v>
+        <v>44.2</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="n">
         <v>1.1</v>
@@ -1236,16 +1236,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>70.5</v>
+        <v>66.5</v>
       </c>
       <c r="F11" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0.2</v>
@@ -1388,19 +1388,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>72.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>24.2</v>
+        <v>33.5</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1419,19 +1419,19 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>64.7</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1450,16 +1450,16 @@
         <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>35.3</v>
+        <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1481,16 +1481,16 @@
         <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>74.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1915,7 +1915,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>25.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2262,13 +2262,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>70.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>42.9</v>
+        <v>41.8</v>
       </c>
       <c r="G3" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="4">
@@ -2290,10 +2290,10 @@
         <v>56.9</v>
       </c>
       <c r="F4" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="G4" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="5">
@@ -2315,10 +2315,10 @@
         <v>36.6</v>
       </c>
       <c r="F5" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -2340,7 +2340,7 @@
         <v>63.3</v>
       </c>
       <c r="F6" t="n">
-        <v>25.9</v>
+        <v>26.1</v>
       </c>
       <c r="G6" t="n">
         <v>11.8</v>
@@ -2365,7 +2365,7 @@
         <v>43.1</v>
       </c>
       <c r="F7" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="G7" t="n">
         <v>7.1</v>
@@ -2384,16 +2384,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>40.4</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2409,16 +2409,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>55.7</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2434,16 +2434,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>22.7</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -2459,16 +2459,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>59.6</v>
+        <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>18.6</v>
+        <v>31.1</v>
       </c>
       <c r="F11" t="n">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>
@@ -2544,7 +2544,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -2594,7 +2594,7 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2987,7 +2987,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>55.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3037,7 +3037,7 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -4041,10 +4041,10 @@
         <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="H2" t="n">
-        <v>67.3</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="3">
@@ -4066,13 +4066,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>70.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="G3" t="n">
-        <v>38.8</v>
+        <v>37.7</v>
       </c>
       <c r="H3" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="4">
@@ -4094,13 +4094,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>38.1</v>
+        <v>39.5</v>
       </c>
       <c r="G4" t="n">
-        <v>16.4</v>
+        <v>16.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -4122,13 +4122,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
@@ -4147,16 +4147,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>61.4</v>
+        <v>74.2</v>
       </c>
       <c r="F6" t="n">
-        <v>25.2</v>
+        <v>30.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -4175,16 +4175,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>76.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F7" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="G7" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -4203,16 +4203,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>61.3</v>
+        <v>53.4</v>
       </c>
       <c r="F8" t="n">
-        <v>20.2</v>
+        <v>17.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -4237,7 +4237,7 @@
         <v>6.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
         <v>0.5</v>
@@ -4284,19 +4284,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>28.4</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4312,19 +4312,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>67.7</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>19.3</v>
+        <v>46.6</v>
       </c>
       <c r="F12" t="n">
-        <v>8.699999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -4340,19 +4340,19 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>55.5</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -4368,19 +4368,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>44.5</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>15.8</v>
+        <v>23.3</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -4396,16 +4396,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -4424,19 +4424,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36.3</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>10.3</v>
+        <v>25.9</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4855,7 +4855,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>65.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -4899,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>34.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6439,10 +6439,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>31.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="3">
@@ -6464,10 +6464,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>76.5</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>55.4</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="4">
@@ -6489,10 +6489,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6514,10 +6514,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7513,13 +7513,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>65.8</v>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="H2" t="n">
-        <v>28.7</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="3">
@@ -7541,13 +7541,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>51.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>21.9</v>
+        <v>28</v>
       </c>
       <c r="H3" t="n">
-        <v>8.800000000000001</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="4">
@@ -7572,10 +7572,10 @@
         <v>69</v>
       </c>
       <c r="G4" t="n">
-        <v>45.5</v>
+        <v>46.9</v>
       </c>
       <c r="H4" t="n">
-        <v>25.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -7600,7 +7600,7 @@
         <v>46.3</v>
       </c>
       <c r="G5" t="n">
-        <v>17.4</v>
+        <v>17.1</v>
       </c>
       <c r="H5" t="n">
         <v>7.5</v>
@@ -7628,10 +7628,10 @@
         <v>53.7</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="7">
@@ -7656,10 +7656,10 @@
         <v>31.1</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="8">
@@ -7678,16 +7678,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" t="n">
         <v>34.1</v>
       </c>
-      <c r="F8" t="n">
-        <v>11.7</v>
-      </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7706,16 +7706,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>69.5</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>34.2</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>17.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="10">
@@ -7734,16 +7734,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>65.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>36.5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -7790,16 +7790,16 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>30.5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -8481,7 +8481,7 @@
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>73.40000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -8543,7 +8543,7 @@
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>26.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8887,10 +8887,10 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>76.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>44.8</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -8909,10 +8909,10 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>80.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -8931,10 +8931,10 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8953,10 +8953,10 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -9473,13 +9473,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>86</v>
+        <v>88.3</v>
       </c>
       <c r="G2" t="n">
-        <v>60.9</v>
+        <v>62.2</v>
       </c>
       <c r="H2" t="n">
-        <v>40.6</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="3">
@@ -9501,13 +9501,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>77.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>56.5</v>
+        <v>55</v>
       </c>
       <c r="H3" t="n">
-        <v>28.3</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="4">
@@ -9529,13 +9529,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="G4" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="5">
@@ -9557,13 +9557,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>51.1</v>
+        <v>50.4</v>
       </c>
       <c r="G5" t="n">
-        <v>17.3</v>
+        <v>16.9</v>
       </c>
       <c r="H5" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -9582,16 +9582,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>43.6</v>
+        <v>45.2</v>
       </c>
       <c r="G6" t="n">
-        <v>17.2</v>
+        <v>17.4</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="7">
@@ -9610,16 +9610,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>22.6</v>
+        <v>21.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -9638,13 +9638,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>37.9</v>
+        <v>32.1</v>
       </c>
       <c r="F8" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0.4</v>
@@ -9666,10 +9666,10 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>52.3</v>
+        <v>59.2</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
         <v>1.6</v>
@@ -9691,19 +9691,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>43.1</v>
+        <v>19.1</v>
       </c>
       <c r="F10" t="n">
-        <v>7.4</v>
+        <v>4.4</v>
       </c>
       <c r="G10" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -9719,19 +9719,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>80.7</v>
+        <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>14.6</v>
+        <v>18.3</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -9747,19 +9747,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>50.5</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -9775,19 +9775,19 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>36.2</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -9803,19 +9803,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>63.8</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9831,19 +9831,19 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>49.5</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>16.4</v>
+        <v>40.8</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -9859,16 +9859,16 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -9887,13 +9887,13 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -10298,10 +10298,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>63.5</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -10348,10 +10348,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -10373,10 +10373,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>36.5</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>14.1</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="6">
@@ -10448,10 +10448,10 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>57.2</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>29.4</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="9">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -507,13 +507,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="H2" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -535,13 +535,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>81.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>63.1</v>
+        <v>63.9</v>
       </c>
       <c r="H3" t="n">
-        <v>36.1</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="4">
@@ -563,13 +563,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="G4" t="n">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>58.8</v>
+        <v>59.2</v>
       </c>
       <c r="G5" t="n">
         <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="6">
@@ -616,16 +616,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>75.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>35.7</v>
+        <v>31.9</v>
       </c>
       <c r="G6" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="7">
@@ -644,16 +644,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>70.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>39.1</v>
+        <v>47.7</v>
       </c>
       <c r="G7" t="n">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="8">
@@ -672,16 +672,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
@@ -700,13 +700,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
@@ -728,16 +728,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>72.5</v>
+        <v>72.7</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="G10" t="n">
         <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -756,13 +756,13 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>47.5</v>
+        <v>46.7</v>
       </c>
       <c r="F11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H11" t="n">
         <v>0.8</v>
@@ -781,19 +781,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -809,16 +809,16 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>33.2</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -837,19 +837,19 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>66.8</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>18.4</v>
+        <v>31.9</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -865,16 +865,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2</v>
+        <v>14.6</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -963,13 +963,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="H2" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="I2" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="3">
@@ -994,13 +994,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>43.8</v>
+        <v>42.3</v>
       </c>
       <c r="H3" t="n">
-        <v>20.8</v>
+        <v>19.6</v>
       </c>
       <c r="I3" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4">
@@ -1025,13 +1025,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="I4" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="5">
@@ -1056,13 +1056,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>72.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>34.9</v>
+        <v>34.1</v>
       </c>
       <c r="I5" t="n">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="6">
@@ -1084,16 +1084,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>74.8</v>
+        <v>72.8</v>
       </c>
       <c r="G6" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -1115,16 +1115,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>77.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="G7" t="n">
-        <v>21.2</v>
+        <v>23.2</v>
       </c>
       <c r="H7" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -1146,16 +1146,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>81</v>
+        <v>83.7</v>
       </c>
       <c r="G8" t="n">
-        <v>51</v>
+        <v>53.3</v>
       </c>
       <c r="H8" t="n">
-        <v>27.4</v>
+        <v>28.8</v>
       </c>
       <c r="I8" t="n">
-        <v>11.9</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="9">
@@ -1177,16 +1177,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>52.7</v>
+        <v>44.5</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>10.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="10">
@@ -1205,19 +1205,19 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>82.5</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>44.2</v>
+        <v>55.5</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>10.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
@@ -1236,19 +1236,19 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>66.5</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1267,19 +1267,19 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>66.8</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1298,19 +1298,19 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>57.6</v>
+        <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>15.4</v>
+        <v>27.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -1329,19 +1329,19 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1360,16 +1360,16 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>33.2</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>5.2</v>
+        <v>16.2</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1391,19 +1391,19 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>33.5</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>16.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="H16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1453,13 +1453,13 @@
         <v>100</v>
       </c>
       <c r="E18" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1569,10 +1569,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>59.7</v>
+        <v>58.8</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="3">
@@ -1594,10 +1594,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>61.7</v>
+        <v>65.2</v>
       </c>
       <c r="G3" t="n">
-        <v>29.8</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="4">
@@ -1616,13 +1616,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>39.5</v>
+        <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="5">
@@ -1641,13 +1641,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="F5" t="n">
-        <v>14.9</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="6">
@@ -1663,16 +1663,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>73.2</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>47.4</v>
+        <v>63.7</v>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>28.2</v>
       </c>
       <c r="G6" t="n">
-        <v>12.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="7">
@@ -1688,16 +1688,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>24.6</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>8.1</v>
+        <v>19.4</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="8">
@@ -1713,16 +1713,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1738,16 +1738,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>26.8</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2237,13 +2237,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>77.3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>51.9</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>32.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2262,13 +2262,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>68.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>41.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>23.8</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="4">
@@ -2287,13 +2287,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>56.9</v>
+        <v>56.7</v>
       </c>
       <c r="F4" t="n">
-        <v>26.1</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>11.3</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="5">
@@ -2312,13 +2312,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="F5" t="n">
-        <v>14.3</v>
+        <v>23.8</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6">
@@ -2337,13 +2337,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>63.3</v>
+        <v>63.8</v>
       </c>
       <c r="F6" t="n">
-        <v>26.1</v>
+        <v>40.7</v>
       </c>
       <c r="G6" t="n">
-        <v>11.8</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="7">
@@ -2362,13 +2362,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="F7" t="n">
-        <v>18.5</v>
+        <v>15.6</v>
       </c>
       <c r="G7" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8">
@@ -2437,13 +2437,13 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>22.7</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>7.6</v>
+        <v>35.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="11">
@@ -2462,13 +2462,13 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2851,10 +2851,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>73.59999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="3">
@@ -2870,10 +2870,10 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2889,10 +2889,10 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="5">
@@ -2908,10 +2908,10 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>26.4</v>
+        <v>27.1</v>
       </c>
       <c r="E5" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -3277,10 +3277,10 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>80.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>71.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -3296,13 +3296,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3318,13 +3318,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="E4" t="n">
-        <v>23.7</v>
+        <v>26.4</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="5">
@@ -3340,13 +3340,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>16.4</v>
+        <v>16.7</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="6">
@@ -3362,13 +3362,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="7">
@@ -3384,13 +3384,13 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="E7" t="n">
-        <v>29.6</v>
+        <v>30.4</v>
       </c>
       <c r="F7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="8">
@@ -3406,13 +3406,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>18.6</v>
+        <v>43.2</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>
@@ -3474,10 +3474,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>83.3</v>
+        <v>83.7</v>
       </c>
       <c r="E2" t="n">
-        <v>57.8</v>
+        <v>58.7</v>
       </c>
       <c r="F2" t="n">
         <v>24.8</v>
@@ -3496,13 +3496,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="E3" t="n">
-        <v>77.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>55.8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -3518,13 +3518,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>73.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="E4" t="n">
-        <v>16.5</v>
+        <v>16.1</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5">
@@ -3540,10 +3540,10 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>57.1</v>
+        <v>57.6</v>
       </c>
       <c r="E5" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -3562,13 +3562,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
       <c r="E6" t="n">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
       <c r="F6" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -3584,10 +3584,10 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>26.6</v>
+        <v>27.5</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="F7" t="n">
         <v>0.9</v>
@@ -3606,10 +3606,10 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F8" t="n">
         <v>0.5</v>
@@ -3628,13 +3628,13 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16.3</v>
       </c>
       <c r="E9" t="n">
         <v>5.4</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -4038,13 +4038,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
+        <v>88.3</v>
       </c>
       <c r="G2" t="n">
-        <v>80.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>67.5</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -4066,13 +4066,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>68.7</v>
+        <v>66.8</v>
       </c>
       <c r="G3" t="n">
-        <v>37.7</v>
+        <v>35.1</v>
       </c>
       <c r="H3" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4">
@@ -4094,13 +4094,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>39.5</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>16.8</v>
+        <v>13.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -4122,13 +4122,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="6">
@@ -4147,16 +4147,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>74.2</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>30.3</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -4175,16 +4175,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>52.3</v>
+        <v>68</v>
       </c>
       <c r="G7" t="n">
-        <v>31.5</v>
+        <v>40.3</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="8">
@@ -4203,16 +4203,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>53.4</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>17.6</v>
+        <v>33.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -4231,16 +4231,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>6.7</v>
+        <v>11.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -4259,16 +4259,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4315,16 +4315,16 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>46.6</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4371,16 +4371,16 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4427,16 +4427,16 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4506,13 +4506,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>76.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="3">
@@ -4531,13 +4531,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>72.8</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>35.2</v>
+        <v>34.4</v>
       </c>
       <c r="G3" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="4">
@@ -4556,13 +4556,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>58.4</v>
+        <v>88.3</v>
       </c>
       <c r="F4" t="n">
-        <v>34.2</v>
+        <v>52.9</v>
       </c>
       <c r="G4" t="n">
-        <v>16.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="5">
@@ -4581,13 +4581,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>55.2</v>
+        <v>53.2</v>
       </c>
       <c r="F5" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="G5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -4603,16 +4603,16 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>44.6</v>
+        <v>46.8</v>
       </c>
       <c r="F6" t="n">
-        <v>15.7</v>
+        <v>16.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="7">
@@ -4628,16 +4628,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>88.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>40.3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4653,16 +4653,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>22.7</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>7.3</v>
+        <v>11.3</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -4678,16 +4678,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>50.2</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9</v>
+        <v>22.9</v>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -4703,16 +4703,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>49.8</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -4728,16 +4728,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -4753,16 +4753,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>11.6</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>11.7</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13">
@@ -4778,10 +4778,10 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -5361,7 +5361,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>33.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -5411,7 +5411,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>66.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5639,10 +5639,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>82.2</v>
+        <v>80.7</v>
       </c>
       <c r="G2" t="n">
-        <v>57.5</v>
+        <v>56.6</v>
       </c>
       <c r="H2" t="n">
         <v>37.2</v>
@@ -5667,13 +5667,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>43.1</v>
+        <v>42.5</v>
       </c>
       <c r="H3" t="n">
-        <v>21.7</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="4">
@@ -5695,7 +5695,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="G4" t="n">
         <v>33.1</v>
@@ -5723,13 +5723,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>52.3</v>
+        <v>51.1</v>
       </c>
       <c r="G5" t="n">
         <v>19.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -5748,13 +5748,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>67.8</v>
+        <v>63.8</v>
       </c>
       <c r="F6" t="n">
-        <v>35.9</v>
+        <v>34.1</v>
       </c>
       <c r="G6" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="H6" t="n">
         <v>6.2</v>
@@ -5776,16 +5776,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>62.8</v>
+        <v>56.6</v>
       </c>
       <c r="F7" t="n">
-        <v>21.3</v>
+        <v>19.3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -5804,16 +5804,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>61.7</v>
+        <v>72.3</v>
       </c>
       <c r="F8" t="n">
-        <v>21.2</v>
+        <v>24.7</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9">
@@ -5832,16 +5832,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>39.3</v>
+        <v>33.6</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10">
@@ -5857,19 +5857,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>74.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>11.8</v>
+        <v>15.4</v>
       </c>
       <c r="G10" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -5885,19 +5885,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>73.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -5913,19 +5913,19 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>76.8</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>32.9</v>
+        <v>43.4</v>
       </c>
       <c r="F12" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="13">
@@ -5941,19 +5941,19 @@
         <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>80.5</v>
+        <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>29.6</v>
+        <v>36.2</v>
       </c>
       <c r="F13" t="n">
-        <v>11.7</v>
+        <v>14.8</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -5969,13 +5969,13 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>100</v>
       </c>
       <c r="D15" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -6025,19 +6025,19 @@
         <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>26.9</v>
+        <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4</v>
+        <v>27.7</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -6053,19 +6053,19 @@
         <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6442,7 +6442,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>32.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -6467,7 +6467,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>67.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -7513,13 +7513,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>65.8</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7541,13 +7541,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>65.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>28</v>
+        <v>42.5</v>
       </c>
       <c r="H3" t="n">
-        <v>11.3</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="4">
@@ -7569,13 +7569,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>69</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>46.9</v>
+        <v>44.2</v>
       </c>
       <c r="H4" t="n">
-        <v>26</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="5">
@@ -7600,10 +7600,10 @@
         <v>46.3</v>
       </c>
       <c r="G5" t="n">
-        <v>17.1</v>
+        <v>21.7</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6">
@@ -7628,10 +7628,10 @@
         <v>53.7</v>
       </c>
       <c r="G6" t="n">
-        <v>22.4</v>
+        <v>27.4</v>
       </c>
       <c r="H6" t="n">
-        <v>10.4</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="7">
@@ -7656,10 +7656,10 @@
         <v>31.1</v>
       </c>
       <c r="G7" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="8">
@@ -7681,13 +7681,13 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>34.1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -7709,13 +7709,13 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>34.2</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>17.6</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
-        <v>8.6</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="10">
@@ -7908,10 +7908,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.2</v>
+        <v>80.8</v>
       </c>
       <c r="H2" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="3">
@@ -7936,10 +7936,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="4">
@@ -7961,13 +7961,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>75.3</v>
+        <v>73.3</v>
       </c>
       <c r="G4" t="n">
-        <v>43.8</v>
+        <v>42.4</v>
       </c>
       <c r="H4" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="5">
@@ -7989,13 +7989,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>60.1</v>
+        <v>72.3</v>
       </c>
       <c r="G5" t="n">
-        <v>13.1</v>
+        <v>16.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -8014,16 +8014,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>34.5</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>9.300000000000001</v>
+        <v>13.9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -8042,16 +8042,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>49.9</v>
+        <v>46.7</v>
       </c>
       <c r="F7" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -8067,19 +8067,19 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>65.7</v>
+        <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>35.1</v>
+        <v>53.3</v>
       </c>
       <c r="F8" t="n">
-        <v>10.1</v>
+        <v>15.2</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -8095,19 +8095,19 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>53.5</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -8123,19 +8123,19 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>13.8</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -8151,19 +8151,19 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>34.3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8236,7 +8236,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="G2" t="n">
         <v>46.7</v>
@@ -8261,10 +8261,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="4">
@@ -8283,13 +8283,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>59.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="5">
@@ -8308,13 +8308,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="F5" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -8333,13 +8333,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>27.1</v>
+        <v>27.3</v>
       </c>
       <c r="F6" t="n">
         <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7">
@@ -8355,16 +8355,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>43.1</v>
+        <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>15.6</v>
+        <v>35.9</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>5.8</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
@@ -8380,16 +8380,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>56.9</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8890,7 +8890,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="3">
@@ -8912,7 +8912,7 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="4">
@@ -9473,13 +9473,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>88.3</v>
+        <v>88.2</v>
       </c>
       <c r="G2" t="n">
-        <v>62.2</v>
+        <v>61</v>
       </c>
       <c r="H2" t="n">
-        <v>41.6</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="3">
@@ -9501,13 +9501,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>75.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="G3" t="n">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="H3" t="n">
-        <v>27.4</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="4">
@@ -9529,13 +9529,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>69.2</v>
+        <v>66.2</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>24.3</v>
       </c>
       <c r="H4" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="5">
@@ -9557,13 +9557,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>50.4</v>
+        <v>42.5</v>
       </c>
       <c r="G5" t="n">
-        <v>16.9</v>
+        <v>13.7</v>
       </c>
       <c r="H5" t="n">
-        <v>8.699999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -9582,16 +9582,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>80.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>45.2</v>
+        <v>57.5</v>
       </c>
       <c r="G6" t="n">
-        <v>17.4</v>
+        <v>22.8</v>
       </c>
       <c r="H6" t="n">
-        <v>9.6</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="7">
@@ -9610,16 +9610,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>21.3</v>
+        <v>33.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -9638,16 +9638,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -9666,16 +9666,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>59.2</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>11.8</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -9694,16 +9694,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -9722,16 +9722,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>67.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>18.3</v>
+        <v>27.3</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1</v>
+        <v>15.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="12">
@@ -9778,16 +9778,16 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -9834,16 +9834,16 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>40.8</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -9969,13 +9969,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="F2" t="n">
-        <v>66</v>
+        <v>65.5</v>
       </c>
       <c r="G2" t="n">
-        <v>34.8</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="3">
@@ -9994,13 +9994,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>63.4</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>41.3</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="4">
@@ -10019,13 +10019,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
       <c r="G4" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
@@ -10044,13 +10044,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>56.4</v>
+        <v>56.6</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
@@ -10069,13 +10069,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="F6" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -10091,13 +10091,13 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>41.9</v>
+        <v>43.4</v>
       </c>
       <c r="E7" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
         <v>0.3</v>
@@ -10116,13 +10116,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G8" t="n">
         <v>0.9</v>
@@ -10141,16 +10141,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>53.8</v>
+        <v>51.4</v>
       </c>
       <c r="E9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
@@ -10166,13 +10166,13 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>46.2</v>
+        <v>48.6</v>
       </c>
       <c r="E10" t="n">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
         <v>0.7</v>
@@ -10191,16 +10191,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="12">
@@ -10216,16 +10216,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>58.1</v>
+        <v>56.6</v>
       </c>
       <c r="E12" t="n">
-        <v>14.1</v>
+        <v>13.7</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -10376,7 +10376,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -10451,7 +10451,7 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>57.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -47,13 +47,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -72,12 +75,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,42 +459,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -507,13 +519,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.59999999999999</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>54.1</v>
+        <v>52.7</v>
       </c>
       <c r="H2" t="n">
-        <v>34</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="3">
@@ -538,10 +550,10 @@
         <v>81.59999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>63.9</v>
+        <v>63.1</v>
       </c>
       <c r="H3" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="4">
@@ -563,13 +575,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>49.9</v>
+        <v>44.2</v>
       </c>
       <c r="G4" t="n">
-        <v>12.7</v>
+        <v>11.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +603,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>59.2</v>
+        <v>67.8</v>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>26.7</v>
       </c>
       <c r="H5" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="6">
@@ -616,16 +628,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>68.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>31.9</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -644,16 +656,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>85.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>47.7</v>
+        <v>55.8</v>
       </c>
       <c r="G7" t="n">
-        <v>15.5</v>
+        <v>17.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="8">
@@ -672,16 +684,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>53.3</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>9.699999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -700,16 +712,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -728,16 +740,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>19.7</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>13.9</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="11">
@@ -756,16 +768,16 @@
         <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -840,16 +852,16 @@
         <v>100</v>
       </c>
       <c r="E14" t="n">
-        <v>31.9</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>8.800000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="G14" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -868,13 +880,13 @@
         <v>100</v>
       </c>
       <c r="E15" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -895,47 +907,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -963,13 +975,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.2</v>
+        <v>76.8</v>
       </c>
       <c r="H2" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>34.8</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="3">
@@ -994,13 +1006,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>42.3</v>
+        <v>36.4</v>
       </c>
       <c r="H3" t="n">
-        <v>19.6</v>
+        <v>16.8</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="4">
@@ -1025,13 +1037,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>74.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="I4" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="5">
@@ -1056,13 +1068,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>71.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="H5" t="n">
-        <v>34.1</v>
+        <v>32.7</v>
       </c>
       <c r="I5" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="6">
@@ -1084,16 +1096,16 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>72.8</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>23.4</v>
+        <v>32.3</v>
       </c>
       <c r="H6" t="n">
-        <v>7.4</v>
+        <v>10.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -1115,16 +1127,16 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="H7" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1146,16 +1158,16 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>83.7</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>53.3</v>
+        <v>63.6</v>
       </c>
       <c r="H8" t="n">
-        <v>28.8</v>
+        <v>34.5</v>
       </c>
       <c r="I8" t="n">
-        <v>12.6</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="9">
@@ -1177,16 +1189,16 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>44.5</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>10.4</v>
+        <v>23.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>7.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -1208,16 +1220,16 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>55.5</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1301,16 +1313,16 @@
         <v>100</v>
       </c>
       <c r="F13" t="n">
-        <v>27.2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1363,13 +1375,13 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>16.2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1394,16 +1406,16 @@
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1514,37 +1526,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1569,10 +1581,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>58.8</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>35.6</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="3">
@@ -1594,10 +1606,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>65.2</v>
+        <v>63.8</v>
       </c>
       <c r="G3" t="n">
-        <v>31.3</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="4">
@@ -1616,13 +1628,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>15.4</v>
+        <v>36.2</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="5">
@@ -1641,13 +1653,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>36.3</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="6">
@@ -1666,13 +1678,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>63.7</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>28.2</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1691,13 +1703,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>19.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1765,42 +1777,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2185,37 +2197,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2265,10 +2277,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>65.40000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="G3" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="4">
@@ -2287,13 +2299,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2312,13 +2324,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>36.2</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>23.8</v>
+        <v>65.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="6">
@@ -2337,13 +2349,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>63.8</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2362,13 +2374,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>43.3</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>15.6</v>
+        <v>35.8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="8">
@@ -2440,10 +2452,10 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>35.5</v>
+        <v>34.2</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2486,37 +2498,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2812,27 +2824,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2929,37 +2941,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3230,32 +3242,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3277,10 +3289,10 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>80.09999999999999</v>
+        <v>88.2</v>
       </c>
       <c r="F2" t="n">
-        <v>72.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3318,13 +3330,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>46.6</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>26.4</v>
+        <v>56.8</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="5">
@@ -3340,13 +3352,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>72.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3362,13 +3374,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>27.6</v>
+        <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2</v>
+        <v>11.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -3384,13 +3396,13 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3412,7 +3424,7 @@
         <v>43.2</v>
       </c>
       <c r="F8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
     </row>
   </sheetData>
@@ -3430,32 +3442,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3474,13 +3486,13 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>83.7</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>58.7</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>24.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3496,13 +3508,13 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="4">
@@ -3518,13 +3530,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>72.5</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>16.1</v>
+        <v>22.9</v>
       </c>
       <c r="F4" t="n">
-        <v>6.7</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="5">
@@ -3540,13 +3552,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>57.6</v>
+        <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>22.5</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6">
@@ -3562,13 +3574,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>42.4</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3584,13 +3596,13 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3606,13 +3618,13 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3628,13 +3640,13 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>16.3</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>5.4</v>
+        <v>32.9</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
     </row>
   </sheetData>
@@ -3652,37 +3664,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3978,42 +3990,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4038,13 +4050,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>79.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>65.90000000000001</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="3">
@@ -4066,13 +4078,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>66.8</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>35.1</v>
+        <v>59.3</v>
       </c>
       <c r="H3" t="n">
-        <v>9.5</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="4">
@@ -4094,13 +4106,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>13.4</v>
+        <v>40.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5">
@@ -4122,13 +4134,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4150,13 +4162,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>10.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="7">
@@ -4178,13 +4190,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>40.3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4206,13 +4218,13 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>33.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11.2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4234,13 +4246,13 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4454,37 +4466,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4506,13 +4518,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>77.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>72.7</v>
       </c>
       <c r="G2" t="n">
-        <v>36.9</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="3">
@@ -4531,13 +4543,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>34.4</v>
+        <v>46.6</v>
       </c>
       <c r="G3" t="n">
-        <v>16.3</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4">
@@ -4556,13 +4568,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>88.3</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>52.9</v>
+        <v>53.4</v>
       </c>
       <c r="G4" t="n">
-        <v>25.5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="5">
@@ -4581,13 +4593,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>53.2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4606,13 +4618,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>46.8</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>16.9</v>
+        <v>27.3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -4656,13 +4668,13 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4681,13 +4693,13 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4756,13 +4768,13 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -4805,32 +4817,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5027,37 +5039,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5278,37 +5290,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5579,42 +5591,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5639,13 +5651,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>80.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>56.6</v>
+        <v>52.1</v>
       </c>
       <c r="H2" t="n">
-        <v>37.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="3">
@@ -5667,13 +5679,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>68.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="G3" t="n">
-        <v>42.5</v>
+        <v>47.6</v>
       </c>
       <c r="H3" t="n">
-        <v>21.1</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="4">
@@ -5695,13 +5707,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>33.1</v>
+        <v>36.4</v>
       </c>
       <c r="H4" t="n">
-        <v>13.9</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="5">
@@ -5723,13 +5735,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>51.1</v>
+        <v>46.6</v>
       </c>
       <c r="G5" t="n">
-        <v>19.4</v>
+        <v>17.7</v>
       </c>
       <c r="H5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -5748,16 +5760,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>63.8</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>34.1</v>
+        <v>53.4</v>
       </c>
       <c r="G6" t="n">
-        <v>11.7</v>
+        <v>20.6</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="7">
@@ -5776,16 +5788,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>56.6</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -5804,16 +5816,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>72.3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>24.7</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>12.3</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -5832,16 +5844,16 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>33.6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5860,16 +5872,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>66.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>15.4</v>
+        <v>23.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="11">
@@ -5916,16 +5928,16 @@
         <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>43.4</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>12</v>
+        <v>27.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3.7</v>
+        <v>10.3</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5944,16 +5956,16 @@
         <v>100</v>
       </c>
       <c r="E13" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -6028,16 +6040,16 @@
         <v>100</v>
       </c>
       <c r="E16" t="n">
-        <v>27.7</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>6.4</v>
+        <v>23.3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -6083,37 +6095,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6384,37 +6396,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6635,37 +6647,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6911,52 +6923,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_R4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7453,42 +7465,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7544,10 +7556,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>42.5</v>
+        <v>35.9</v>
       </c>
       <c r="H3" t="n">
-        <v>20.1</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="4">
@@ -7569,13 +7581,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>68.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>44.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>28.6</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="5">
@@ -7597,13 +7609,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>46.3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7625,13 +7637,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>53.7</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>27.4</v>
+        <v>51.3</v>
       </c>
       <c r="H6" t="n">
-        <v>12.6</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="7">
@@ -7653,13 +7665,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7712,10 +7724,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="H9" t="n">
-        <v>23.6</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="10">
@@ -7845,42 +7857,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7908,10 +7920,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>80.8</v>
+        <v>81.3</v>
       </c>
       <c r="H2" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="3">
@@ -7936,10 +7948,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="H3" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="4">
@@ -7961,13 +7973,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>73.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>42.4</v>
+        <v>43.6</v>
       </c>
       <c r="H4" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="5">
@@ -7989,13 +8001,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>72.3</v>
+        <v>72.8</v>
       </c>
       <c r="G5" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6">
@@ -8014,16 +8026,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>13.9</v>
+        <v>27.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -8042,16 +8054,16 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>46.7</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>11.5</v>
+        <v>24.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8">
@@ -8070,16 +8082,16 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>53.3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8126,16 +8138,16 @@
         <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -8181,37 +8193,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8236,10 +8248,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>77.3</v>
+        <v>71.7</v>
       </c>
       <c r="G2" t="n">
-        <v>46.7</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="3">
@@ -8261,10 +8273,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>79.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>39.9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -8283,13 +8295,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>64.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>14.8</v>
+        <v>24.9</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5">
@@ -8308,13 +8320,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>20.6</v>
+        <v>28.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -8333,13 +8345,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8358,13 +8370,13 @@
         <v>100</v>
       </c>
       <c r="E7" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8407,47 +8419,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8840,32 +8852,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9062,37 +9074,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9413,42 +9425,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9473,13 +9485,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>61</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>41.1</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="3">
@@ -9501,13 +9513,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>52.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>25.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -9529,13 +9541,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>66.2</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>24.3</v>
+        <v>32.1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -9557,13 +9569,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -9585,13 +9597,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>22.8</v>
+        <v>34.1</v>
       </c>
       <c r="H6" t="n">
-        <v>13.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="7">
@@ -9613,13 +9625,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>33.8</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9669,13 +9681,13 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -9725,13 +9737,13 @@
         <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -9917,37 +9929,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9969,13 +9981,13 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>83.7</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>65.5</v>
+        <v>75.7</v>
       </c>
       <c r="G2" t="n">
-        <v>35.5</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="3">
@@ -9994,13 +10006,13 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>63</v>
+        <v>85.2</v>
       </c>
       <c r="G3" t="n">
-        <v>40.3</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="4">
@@ -10019,13 +10031,13 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>78.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -10044,13 +10056,13 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>56.6</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5</v>
+        <v>24.3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="6">
@@ -10069,13 +10081,13 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>43.4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -10091,16 +10103,16 @@
         <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>43.4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -10116,16 +10128,16 @@
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>55.7</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -10141,16 +10153,16 @@
         <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -10166,16 +10178,16 @@
         <v>100</v>
       </c>
       <c r="D10" t="n">
-        <v>48.6</v>
+        <v>100</v>
       </c>
       <c r="E10" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -10191,16 +10203,16 @@
         <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
       <c r="E11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -10216,16 +10228,16 @@
         <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>56.6</v>
+        <v>100</v>
       </c>
       <c r="E12" t="n">
-        <v>13.7</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>14.8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -10243,37 +10255,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10544,37 +10556,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,42 +447,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -907,47 +895,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1526,37 +1514,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1777,42 +1765,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2197,37 +2185,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2498,37 +2486,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2824,27 +2812,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2941,37 +2929,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3242,32 +3230,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3442,32 +3430,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3664,37 +3652,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3990,42 +3978,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4466,37 +4454,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4817,32 +4805,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5039,37 +5027,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5290,37 +5278,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5591,42 +5579,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6095,37 +6083,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6396,37 +6384,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6647,37 +6635,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6923,52 +6911,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_R4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7465,42 +7453,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7857,42 +7845,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8193,37 +8181,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8419,47 +8407,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8852,32 +8840,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9074,37 +9062,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9425,42 +9413,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9929,37 +9917,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10255,37 +10243,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10556,37 +10544,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -507,13 +507,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>52.7</v>
+        <v>66.7</v>
       </c>
       <c r="H2" t="n">
-        <v>33.2</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="3">
@@ -535,13 +535,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>81.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>63.1</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>36.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -563,13 +563,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>44.2</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>11.1</v>
+        <v>18.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="5">
@@ -591,13 +591,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>67.8</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="H5" t="n">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="6">
@@ -647,13 +647,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>55.8</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -675,13 +675,13 @@
         <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -731,13 +731,13 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -843,13 +843,13 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>32.2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -963,13 +963,13 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>76.8</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>33.5</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="3">
@@ -994,13 +994,13 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>16.8</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1025,13 +1025,13 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>72.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>38.7</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>17.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1056,13 +1056,13 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>67.7</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1087,13 +1087,13 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>32.3</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>25.9</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="7">
@@ -1118,13 +1118,13 @@
         <v>100</v>
       </c>
       <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
         <v>27.6</v>
       </c>
-      <c r="H7" t="n">
-        <v>10.1</v>
-      </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="8">
@@ -1149,13 +1149,13 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>34.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>15.2</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="9">
@@ -1180,13 +1180,13 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1569,10 +1569,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>39.2</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="3">
@@ -1594,10 +1594,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>63.8</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>32.3</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="4">
@@ -1619,10 +1619,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1644,10 +1644,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2265,10 +2265,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>64.2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>45.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2315,10 +2315,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>65.8</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>23.4</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="6">
@@ -2365,10 +2365,10 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>35.8</v>
+        <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>21.4</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="8">
@@ -2440,10 +2440,10 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>34.2</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -3277,10 +3277,10 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>88.2</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>79.40000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="3">
@@ -3321,10 +3321,10 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>56.8</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>9.4</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="5">
@@ -3365,10 +3365,10 @@
         <v>100</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3409,10 +3409,10 @@
         <v>100</v>
       </c>
       <c r="E8" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3499,10 +3499,10 @@
         <v>100</v>
       </c>
       <c r="E3" t="n">
-        <v>77.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>64.2</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -3521,10 +3521,10 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3543,10 +3543,10 @@
         <v>100</v>
       </c>
       <c r="E5" t="n">
-        <v>67.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>17.1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -3631,10 +3631,10 @@
         <v>100</v>
       </c>
       <c r="E9" t="n">
-        <v>32.9</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4041,10 +4041,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>89.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>76.2</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -4069,10 +4069,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>59.3</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>13.3</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="4">
@@ -4097,10 +4097,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4153,10 +4153,10 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4509,10 +4509,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>46.6</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="3">
@@ -4534,10 +4534,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>46.6</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>20.3</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="4">
@@ -4559,10 +4559,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4609,10 +4609,10 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5639,13 +5639,13 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>76.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>52.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>33.8</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="3">
@@ -5667,13 +5667,13 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>76.7</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>47.6</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5695,13 +5695,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>36.4</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>15.5</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="5">
@@ -5723,13 +5723,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>46.6</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>17.7</v>
+        <v>33.9</v>
       </c>
       <c r="H5" t="n">
-        <v>8.9</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="6">
@@ -5751,13 +5751,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>53.4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5863,13 +5863,13 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5919,13 +5919,13 @@
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -6031,13 +6031,13 @@
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>23.3</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7</v>
+        <v>23.1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17">
@@ -7544,10 +7544,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>16.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7572,10 +7572,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>64.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>41.2</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="5">
@@ -7628,10 +7628,10 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>51.3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>21.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7712,10 +7712,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>48.7</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>20.5</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="10">
@@ -7908,10 +7908,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>81.3</v>
+        <v>92.3</v>
       </c>
       <c r="H2" t="n">
-        <v>52.4</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="3">
@@ -7936,10 +7936,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>49.4</v>
+        <v>44.3</v>
       </c>
       <c r="H3" t="n">
-        <v>19.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="4">
@@ -7961,13 +7961,13 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>75.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>43.6</v>
+        <v>55.7</v>
       </c>
       <c r="H4" t="n">
-        <v>20.7</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="5">
@@ -7989,13 +7989,13 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>72.8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8017,13 +8017,13 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>27.2</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -8045,13 +8045,13 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>24.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8236,10 +8236,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>43.7</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="3">
@@ -8261,10 +8261,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>75.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>39</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="4">
@@ -8286,10 +8286,10 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>24.9</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8311,10 +8311,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -9476,10 +9476,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>65.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>42.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
@@ -9504,10 +9504,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>67.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -9532,10 +9532,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -9588,10 +9588,10 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>34.1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9972,10 +9972,10 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>75.7</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>36.7</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="3">
@@ -9997,10 +9997,10 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>85.2</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>53.9</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="4">
@@ -10047,10 +10047,10 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -10222,10 +10222,10 @@
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -510,10 +510,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>39.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -538,10 +538,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>44</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="4">
@@ -566,10 +566,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -594,10 +594,10 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="6">
@@ -966,10 +966,10 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>74.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>46.7</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="3">
@@ -1090,10 +1090,10 @@
         <v>100</v>
       </c>
       <c r="H6" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1121,10 +1121,10 @@
         <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1152,10 +1152,10 @@
         <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>72.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>35.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="9">
@@ -1572,7 +1572,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>56.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1597,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>43.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -2318,7 +2318,7 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>44.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2368,7 +2368,7 @@
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>55.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -2851,10 +2851,10 @@
         <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>72.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>55.7</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="3">
@@ -2870,10 +2870,10 @@
         <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2889,10 +2889,10 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>14.8</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="5">
@@ -2908,10 +2908,10 @@
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3280,7 +3280,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>88.3</v>
+        <v>85.40000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3324,7 +3324,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>11.7</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="5">
@@ -3502,7 +3502,7 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -3546,7 +3546,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4044,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>80.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -4072,7 +4072,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>19.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -4512,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>63.9</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -4537,7 +4537,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5642,10 +5642,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>66.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>47.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -5698,10 +5698,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>76.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>30.6</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="5">
@@ -5726,10 +5726,10 @@
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>33.9</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>18.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="6">
@@ -6034,10 +6034,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>23.1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -7575,7 +7575,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7715,7 +7715,7 @@
         <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>40.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -7908,10 +7908,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>57.4</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="3">
@@ -7936,10 +7936,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>16.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="4">
@@ -7964,10 +7964,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>55.7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>25.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8020,10 +8020,10 @@
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8239,7 +8239,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>55.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -8264,7 +8264,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>44.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -8890,7 +8890,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -8912,7 +8912,7 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -9479,7 +9479,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -9507,7 +9507,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -9975,7 +9975,7 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -10000,7 +10000,7 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>55.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -47,13 +47,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -64,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -72,12 +75,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,42 +459,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -895,47 +907,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1514,37 +1526,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1765,42 +1777,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2185,37 +2197,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2486,37 +2498,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2812,27 +2824,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2854,7 +2866,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>75.8</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="3">
@@ -2892,7 +2904,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>24.2</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="5">
@@ -2929,37 +2941,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3230,32 +3242,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3430,32 +3442,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3652,37 +3664,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3978,42 +3990,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4454,37 +4466,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4805,32 +4817,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5027,37 +5039,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5278,37 +5290,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5579,42 +5591,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5701,7 +5713,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>50.7</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="5">
@@ -5729,7 +5741,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>49.3</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="6">
@@ -6083,37 +6095,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6384,37 +6396,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6635,37 +6647,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6911,52 +6923,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_R4</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7453,42 +7465,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7845,42 +7857,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7911,7 +7923,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>66.2</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="3">
@@ -7939,7 +7951,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>33.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="4">
@@ -8181,37 +8193,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8407,47 +8419,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8840,32 +8852,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9062,37 +9074,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9413,42 +9425,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9917,37 +9929,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10243,37 +10255,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10544,37 +10556,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,42 +447,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -907,47 +895,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1526,37 +1514,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1777,42 +1765,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2197,37 +2185,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2498,37 +2486,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2824,27 +2812,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2866,7 +2854,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>72.8</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="3">
@@ -2904,7 +2892,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>27.2</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="5">
@@ -2941,37 +2929,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3242,32 +3230,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3442,32 +3430,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3664,37 +3652,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3990,42 +3978,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4466,37 +4454,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4817,32 +4805,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5039,37 +5027,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5290,37 +5278,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5591,42 +5579,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5713,7 +5701,7 @@
         <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>53.2</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="5">
@@ -5741,7 +5729,7 @@
         <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="6">
@@ -6095,37 +6083,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6396,37 +6384,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6647,37 +6635,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6923,52 +6911,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_R4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7465,42 +7453,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7857,42 +7845,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7923,7 +7911,7 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>67.8</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="3">
@@ -7951,7 +7939,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>32.2</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="4">
@@ -8193,37 +8181,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8419,47 +8407,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8852,32 +8840,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9074,37 +9062,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9425,42 +9413,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9929,37 +9917,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10255,37 +10243,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10556,37 +10544,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>

--- a/conf_tourney_preds_2026.xlsx
+++ b/conf_tourney_preds_2026.xlsx
@@ -47,16 +47,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,21 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,42 +447,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -907,47 +895,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1526,37 +1514,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -1777,42 +1765,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2197,37 +2185,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2498,37 +2486,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2824,27 +2812,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -2866,7 +2854,7 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>72.8</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="3">
@@ -2904,7 +2892,7 @@
         <v>100</v>
       </c>
       <c r="E4" t="n">
-        <v>27.2</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="5">
@@ -2941,37 +2929,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3242,32 +3230,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3442,32 +3430,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3664,37 +3652,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -3990,42 +3978,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4466,37 +4454,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -4817,32 +4805,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5039,37 +5027,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5290,37 +5278,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -5591,42 +5579,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6095,37 +6083,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6396,37 +6384,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6647,37 +6635,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -6923,52 +6911,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_R4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7465,42 +7453,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -7857,42 +7845,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8193,37 +8181,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8419,47 +8407,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_R3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -8852,32 +8840,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9074,37 +9062,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9425,42 +9413,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -9929,37 +9917,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10255,37 +10243,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
@@ -10556,37 +10544,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Seed</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>TeamName</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pct_R1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>pct_QF</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>pct_SF</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>pct_Final</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>pct_Champion</t>
         </is>
